--- a/GORRITI/Junio/GORRITI-JUNIO.xlsx
+++ b/GORRITI/Junio/GORRITI-JUNIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\GORRITI\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8751E49A-3449-4226-B8CA-8DFA1A64E832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133B47CA-19DC-4305-9C02-CBBE2481039F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$R$90</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$147</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$146</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="257">
   <si>
     <t>MAIL: consorciogorriti368@gmail.com</t>
   </si>
@@ -124,9 +124,6 @@
     <t xml:space="preserve">ARCA </t>
   </si>
   <si>
-    <t>PMC 08/05</t>
-  </si>
-  <si>
     <t>Fatheryh</t>
   </si>
   <si>
@@ -157,21 +154,12 @@
     <t>EDESUR - Cliente nro. 01672319</t>
   </si>
   <si>
-    <t>Transf 09/05</t>
-  </si>
-  <si>
     <t>Metrogas - Cliente nro. 020495697900</t>
   </si>
   <si>
     <t>PMC 13/05</t>
   </si>
   <si>
-    <t>Metrogas Plan de pagos cuota 3 de 4 - Cliente nro. 020495697900</t>
-  </si>
-  <si>
-    <t>PMC 14/04</t>
-  </si>
-  <si>
     <t xml:space="preserve">Personal Flow - Debito automatico </t>
   </si>
   <si>
@@ -205,30 +193,18 @@
     <t>Fumigacion Viturro Alberto</t>
   </si>
   <si>
-    <t>Transf 26/05</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ascensores Lema mantenimiento </t>
   </si>
   <si>
     <t>Transf 13/05</t>
   </si>
   <si>
-    <t>Kromacolor - Compra de materiales (pintura, sellador, etc) reparacion techos 12A</t>
-  </si>
-  <si>
     <t>Efectivo</t>
   </si>
   <si>
-    <t>TRANSFERENCIAS A PATRIZIO DIEGO ROBERTO QUE NOSE A QUE GASTO CORRESPONDE</t>
-  </si>
-  <si>
     <t>Tranfs 13/05</t>
   </si>
   <si>
-    <t>HAY DOS COMPROBANTES DE 210.000$ A DOARTERO QUE NOSE SI CORRESPONDEN A GASTOS YA PUESTOS O NO</t>
-  </si>
-  <si>
     <t>Toto calefaccion - Reparacion y cambio de varilla detectora de chispa del quemador y bujia que es la cjispa del encendido -  Mano de obra</t>
   </si>
   <si>
@@ -238,9 +214,6 @@
     <t>Doartero materiales y mano de obra cambuio de lamparas</t>
   </si>
   <si>
-    <t>Doartero materiales y mano de obra reparacion caño de agua principal subida</t>
-  </si>
-  <si>
     <t>Doartero materiales y mano de obra reparacion caño de gas 10A</t>
   </si>
   <si>
@@ -268,9 +241,6 @@
     <t xml:space="preserve">Impresiones de planos </t>
   </si>
   <si>
-    <t>Clean home - Bolsas de consorcio</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -781,9 +751,6 @@
     <t>Sindicatos mes de JUNIO</t>
   </si>
   <si>
-    <t>HONORARIOS ADMINISTRACION RC - SE ABONA EL MES MAYO Y JUNIO</t>
-  </si>
-  <si>
     <t>HONORARIOS ADMINISTRACION RC - SE ABONA EL MES MAYO - SE DEBE JUNIO</t>
   </si>
   <si>
@@ -794,6 +761,42 @@
   </si>
   <si>
     <t>Destapaciones italoamericanas de cañerias deague de cocina y lavadero - mantenimiento de cañerias, repaso de ramales, columnas del 1er piso y sus dos salidas cloacales - Abono febrero, marzo y MAYO</t>
+  </si>
+  <si>
+    <t>Transf 19/06</t>
+  </si>
+  <si>
+    <t>Transf 17/06</t>
+  </si>
+  <si>
+    <t>Transf 13/06</t>
+  </si>
+  <si>
+    <t>Transf 12/06</t>
+  </si>
+  <si>
+    <t>Ascensores Lema - Provision y colocacion de una nueva base original para antenas de freno, para cabezal de freno y una nueva antena con el buje correspondiente de apertura y cierre del ascensor unico que esta andando</t>
+  </si>
+  <si>
+    <t>PMC 09/06</t>
+  </si>
+  <si>
+    <t>PMC 10/06</t>
+  </si>
+  <si>
+    <t>Metrogas Plan de pagos cuota 4 de 4 - Cliente nro. 020495697900</t>
+  </si>
+  <si>
+    <t>Transf 11/06</t>
+  </si>
+  <si>
+    <t>HONORARIOS CONTADOR GUSTAVO PADRON</t>
+  </si>
+  <si>
+    <t>Transf 09/06</t>
+  </si>
+  <si>
+    <t>Doartero soldadura de puerta de acero inoxidable principal</t>
   </si>
 </sst>
 </file>
@@ -1534,7 +1537,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1780,7 +1783,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="168" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="24" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1813,7 +1815,6 @@
     </xf>
     <xf numFmtId="16" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="11" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="11" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="23" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1836,31 +1837,20 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1871,27 +1861,20 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1905,12 +1888,40 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2218,7 +2229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M151"/>
+  <dimension ref="A1:M150"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2284,7 +2295,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="75" t="s">
@@ -2304,49 +2315,49 @@
       <c r="E7" s="21"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="218" t="s">
+      <c r="B9" s="207" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="214"/>
+      <c r="C9" s="208"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="214"/>
-      <c r="C10" s="214"/>
+      <c r="B10" s="208"/>
+      <c r="C10" s="208"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="214"/>
-      <c r="C11" s="214"/>
+      <c r="B11" s="208"/>
+      <c r="C11" s="208"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="215" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="214"/>
-      <c r="C14" s="214"/>
-      <c r="D14" s="214"/>
-      <c r="E14" s="214"/>
+      <c r="B14" s="208"/>
+      <c r="C14" s="208"/>
+      <c r="D14" s="208"/>
+      <c r="E14" s="208"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="214"/>
-      <c r="B15" s="214"/>
-      <c r="C15" s="214"/>
-      <c r="D15" s="214"/>
-      <c r="E15" s="214"/>
+      <c r="A15" s="208"/>
+      <c r="B15" s="208"/>
+      <c r="C15" s="208"/>
+      <c r="D15" s="208"/>
+      <c r="E15" s="208"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="214"/>
-      <c r="B16" s="214"/>
-      <c r="C16" s="214"/>
-      <c r="D16" s="214"/>
-      <c r="E16" s="214"/>
+      <c r="A16" s="208"/>
+      <c r="B16" s="208"/>
+      <c r="C16" s="208"/>
+      <c r="D16" s="208"/>
+      <c r="E16" s="208"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="214"/>
-      <c r="B17" s="214"/>
-      <c r="C17" s="214"/>
-      <c r="D17" s="214"/>
-      <c r="E17" s="214"/>
+      <c r="A17" s="208"/>
+      <c r="B17" s="208"/>
+      <c r="C17" s="208"/>
+      <c r="D17" s="208"/>
+      <c r="E17" s="208"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2377,7 +2388,7 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="169">
+      <c r="D23" s="168">
         <v>1227647</v>
       </c>
       <c r="E23" s="163" t="s">
@@ -2388,14 +2399,14 @@
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="169"/>
+      <c r="D24" s="168"/>
       <c r="E24" s="120"/>
     </row>
     <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="169"/>
+      <c r="D25" s="168"/>
       <c r="E25" s="120"/>
     </row>
     <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2404,7 +2415,7 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="169">
+      <c r="D26" s="168">
         <v>0</v>
       </c>
       <c r="E26" s="120"/>
@@ -2413,7 +2424,7 @@
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="169"/>
+      <c r="D27" s="168"/>
       <c r="E27" s="120"/>
       <c r="G27" s="22"/>
     </row>
@@ -2423,11 +2434,11 @@
       </c>
       <c r="B28" s="60"/>
       <c r="C28" s="60"/>
-      <c r="D28" s="170">
+      <c r="D28" s="169">
         <f>SUM(D23:D27)</f>
         <v>1227647</v>
       </c>
-      <c r="E28" s="171"/>
+      <c r="E28" s="170"/>
       <c r="G28" s="22">
         <f>D28+D37</f>
         <v>2303751</v>
@@ -2439,7 +2450,7 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="169">
+      <c r="D29" s="168">
         <v>1076104</v>
       </c>
       <c r="E29" s="163" t="s">
@@ -2450,21 +2461,21 @@
       <c r="A30" s="29"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="169"/>
+      <c r="D30" s="168"/>
       <c r="E30" s="120"/>
     </row>
     <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="169"/>
+      <c r="D31" s="168"/>
       <c r="E31" s="120"/>
     </row>
     <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="172"/>
+      <c r="D32" s="171"/>
       <c r="E32" s="120"/>
     </row>
     <row r="33" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2473,7 +2484,7 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="172"/>
+      <c r="D33" s="171"/>
       <c r="E33" s="120"/>
     </row>
     <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2482,7 +2493,7 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="172"/>
+      <c r="D34" s="171"/>
       <c r="E34" s="120"/>
     </row>
     <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2491,7 +2502,7 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
-      <c r="D35" s="172">
+      <c r="D35" s="171">
         <v>0</v>
       </c>
       <c r="E35" s="120"/>
@@ -2500,7 +2511,7 @@
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="172"/>
+      <c r="D36" s="171"/>
       <c r="E36" s="120"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -2509,11 +2520,11 @@
       </c>
       <c r="B37" s="60"/>
       <c r="C37" s="60"/>
-      <c r="D37" s="173">
+      <c r="D37" s="172">
         <f>SUM(D29:D36)</f>
         <v>1076104</v>
       </c>
-      <c r="E37" s="171"/>
+      <c r="E37" s="170"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="30" t="s">
@@ -2521,8 +2532,8 @@
       </c>
       <c r="B38" s="30"/>
       <c r="C38" s="30"/>
-      <c r="D38" s="174"/>
-      <c r="E38" s="175">
+      <c r="D38" s="173"/>
+      <c r="E38" s="174">
         <f>D28+D37</f>
         <v>2303751</v>
       </c>
@@ -2534,33 +2545,32 @@
       </c>
       <c r="B39" s="37"/>
       <c r="C39" s="37"/>
-      <c r="D39" s="176"/>
-      <c r="E39" s="177"/>
+      <c r="D39" s="175"/>
+      <c r="E39" s="176"/>
     </row>
     <row r="40" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="221" t="s">
-        <v>251</v>
-      </c>
-      <c r="B40" s="211"/>
-      <c r="C40" s="203"/>
-      <c r="D40" s="169">
-        <f>2*56000</f>
-        <v>112000</v>
-      </c>
-      <c r="E40" s="202" t="s">
-        <v>24</v>
+      <c r="A40" s="214" t="s">
+        <v>254</v>
+      </c>
+      <c r="B40" s="210"/>
+      <c r="C40" s="201"/>
+      <c r="D40" s="240">
+        <v>56000</v>
+      </c>
+      <c r="E40" s="200" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="210" t="s">
-        <v>252</v>
-      </c>
-      <c r="B41" s="211"/>
+      <c r="A41" s="209" t="s">
+        <v>241</v>
+      </c>
+      <c r="B41" s="210"/>
       <c r="C41" s="55"/>
-      <c r="D41" s="169">
+      <c r="D41" s="241">
         <v>249000</v>
       </c>
-      <c r="E41" s="202" t="s">
+      <c r="E41" s="200" t="s">
         <v>24</v>
       </c>
       <c r="H41" s="146"/>
@@ -2571,10 +2581,10 @@
       </c>
       <c r="B42" s="30"/>
       <c r="C42" s="30"/>
-      <c r="D42" s="178"/>
-      <c r="E42" s="179">
+      <c r="D42" s="177"/>
+      <c r="E42" s="178">
         <f>SUM(D40:D41)</f>
-        <v>361000</v>
+        <v>305000</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -2583,28 +2593,28 @@
       </c>
       <c r="B43" s="30"/>
       <c r="C43" s="30"/>
-      <c r="D43" s="180"/>
-      <c r="E43" s="181"/>
+      <c r="D43" s="179"/>
+      <c r="E43" s="180"/>
     </row>
     <row r="44" spans="1:8" s="40" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="212" t="s">
+      <c r="A44" s="211" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="211"/>
+      <c r="B44" s="210"/>
       <c r="C44" s="57"/>
-      <c r="D44" s="182">
+      <c r="D44" s="181">
         <v>120977</v>
       </c>
-      <c r="E44" s="183" t="s">
+      <c r="E44" s="182" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="212"/>
-      <c r="B45" s="211"/>
+      <c r="A45" s="211"/>
+      <c r="B45" s="210"/>
       <c r="C45" s="57"/>
-      <c r="D45" s="184"/>
-      <c r="E45" s="183"/>
+      <c r="D45" s="183"/>
+      <c r="E45" s="182"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="30" t="s">
@@ -2612,7 +2622,7 @@
       </c>
       <c r="B46" s="30"/>
       <c r="C46" s="30"/>
-      <c r="D46" s="178"/>
+      <c r="D46" s="177"/>
       <c r="E46" s="121">
         <f>SUM(D44:D45)</f>
         <v>120977</v>
@@ -2624,8 +2634,8 @@
       </c>
       <c r="B47" s="164"/>
       <c r="C47" s="164"/>
-      <c r="D47" s="185"/>
-      <c r="E47" s="186"/>
+      <c r="D47" s="184"/>
+      <c r="E47" s="185"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
@@ -2633,27 +2643,27 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="55"/>
-      <c r="D48" s="207">
-        <v>1644550.83</v>
-      </c>
-      <c r="E48" s="187" t="s">
-        <v>32</v>
+      <c r="D48" s="239">
+        <v>1688376.15</v>
+      </c>
+      <c r="E48" s="186" t="s">
+        <v>250</v>
       </c>
       <c r="G48" s="146"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" s="5"/>
+      <c r="D49" s="183">
+        <v>129055.15</v>
+      </c>
+      <c r="E49" s="187" t="s">
         <v>33</v>
-      </c>
-      <c r="C49" s="5"/>
-      <c r="D49" s="184">
-        <v>129055.15</v>
-      </c>
-      <c r="E49" s="188" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2662,13 +2672,13 @@
         <v>Sindicatos mes de JUNIO</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C50" s="5"/>
-      <c r="D50" s="184">
+      <c r="D50" s="183">
         <v>234412.98</v>
       </c>
-      <c r="E50" s="188" t="str">
+      <c r="E50" s="187" t="str">
         <f>E49</f>
         <v>Debito 12/05</v>
       </c>
@@ -2679,959 +2689,940 @@
         <v>Sindicatos mes de JUNIO</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C51" s="5"/>
-      <c r="D51" s="184">
+      <c r="D51" s="183">
         <v>14339.47</v>
       </c>
-      <c r="E51" s="189" t="str">
+      <c r="E51" s="188" t="str">
         <f>E50</f>
         <v>Debito 12/05</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B52" s="164"/>
       <c r="C52" s="164"/>
-      <c r="D52" s="190"/>
+      <c r="D52" s="189"/>
       <c r="E52" s="121">
         <f>SUM(D48:D51)</f>
-        <v>2022358.43</v>
+        <v>2066183.7499999998</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" s="164"/>
       <c r="C53" s="164"/>
-      <c r="D53" s="185"/>
-      <c r="E53" s="186"/>
+      <c r="D53" s="184"/>
+      <c r="E53" s="185"/>
     </row>
     <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="184">
-        <v>814908.33</v>
-      </c>
-      <c r="E54" s="200" t="s">
-        <v>24</v>
+      <c r="D54" s="183">
+        <v>907716.3</v>
+      </c>
+      <c r="E54" s="198" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="184">
-        <v>24398.76</v>
-      </c>
-      <c r="E55" s="191" t="str">
-        <f>E54</f>
-        <v>Transf 07/05</v>
+      <c r="D55" s="235">
+        <v>22454.93</v>
+      </c>
+      <c r="E55" s="198" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="184">
-        <v>15117.56</v>
-      </c>
-      <c r="E56" s="191" t="str">
+      <c r="D56" s="235">
+        <v>13452.23</v>
+      </c>
+      <c r="E56" s="190" t="str">
         <f>E55</f>
-        <v>Transf 07/05</v>
+        <v>Transf 13/06</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="184">
-        <v>11961.98</v>
-      </c>
-      <c r="E57" s="200" t="s">
-        <v>43</v>
+      <c r="D57" s="235">
+        <v>11144.38</v>
+      </c>
+      <c r="E57" s="198" t="str">
+        <f>E56</f>
+        <v>Transf 13/06</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
-      <c r="D58" s="184">
-        <v>9656.9599999999991</v>
-      </c>
-      <c r="E58" s="191" t="s">
-        <v>45</v>
+      <c r="D58" s="235">
+        <f>4753.74+5348.66</f>
+        <v>10102.4</v>
+      </c>
+      <c r="E58" s="238" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>46</v>
+        <v>252</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="184">
+      <c r="D59" s="235">
         <v>571919</v>
       </c>
-      <c r="E59" s="191" t="s">
-        <v>47</v>
+      <c r="E59" s="190" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="184">
+      <c r="D60" s="183">
         <v>22050.01</v>
       </c>
-      <c r="E60" s="192" t="s">
-        <v>49</v>
+      <c r="E60" s="191" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="212" t="s">
-        <v>50</v>
-      </c>
-      <c r="B61" s="211"/>
+      <c r="A61" s="211" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" s="210"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="184">
+      <c r="D61" s="183">
         <v>2302294.3199999998</v>
       </c>
-      <c r="E61" s="191" t="s">
-        <v>45</v>
+      <c r="E61" s="190" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="212"/>
-      <c r="B62" s="211"/>
+      <c r="A62" s="211"/>
+      <c r="B62" s="210"/>
       <c r="C62" s="165"/>
-      <c r="D62" s="219"/>
-      <c r="E62" s="211"/>
+      <c r="D62" s="212"/>
+      <c r="E62" s="210"/>
     </row>
     <row r="63" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="30" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B63" s="30"/>
       <c r="C63" s="30"/>
-      <c r="D63" s="178"/>
+      <c r="D63" s="177"/>
       <c r="E63" s="121">
         <f>SUM(D54:D62)</f>
-        <v>3772306.92</v>
+        <v>3861133.5700000003</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="37" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B64" s="30"/>
       <c r="C64" s="30"/>
-      <c r="D64" s="178"/>
-      <c r="E64" s="193"/>
-    </row>
-    <row r="65" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="210" t="s">
-        <v>53</v>
-      </c>
-      <c r="B65" s="211"/>
+      <c r="D64" s="177"/>
+      <c r="E64" s="192"/>
+    </row>
+    <row r="65" spans="1:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="209" t="s">
+        <v>49</v>
+      </c>
+      <c r="B65" s="210"/>
       <c r="C65" s="58"/>
-      <c r="D65" s="184">
+      <c r="D65" s="183">
         <f>72600+360000</f>
         <v>432600</v>
       </c>
       <c r="E65" s="126" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="209" t="s">
+        <v>242</v>
+      </c>
+      <c r="B66" s="210"/>
+      <c r="C66" s="58"/>
+      <c r="D66" s="183">
+        <v>96800</v>
+      </c>
+      <c r="E66" s="126" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="209" t="s">
+        <v>52</v>
+      </c>
+      <c r="B67" s="210"/>
+      <c r="C67" s="58"/>
+      <c r="D67" s="183">
+        <v>38000</v>
+      </c>
+      <c r="E67" s="126" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="B66" s="211"/>
-      <c r="C66" s="58"/>
-      <c r="D66" s="184">
-        <v>96800</v>
-      </c>
-      <c r="E66" s="126" t="s">
+      <c r="B68" s="166"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="235">
+        <v>54600</v>
+      </c>
+      <c r="E68" s="198" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="210" t="s">
-        <v>56</v>
-      </c>
-      <c r="B67" s="211"/>
-      <c r="C67" s="58"/>
-      <c r="D67" s="184">
-        <v>38000</v>
-      </c>
-      <c r="E67" s="126" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="184">
-        <v>52000</v>
-      </c>
-      <c r="E68" s="200" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="B69" s="166"/>
       <c r="C69" s="5"/>
-      <c r="D69" s="184">
-        <v>53500</v>
-      </c>
-      <c r="E69" s="200" t="s">
+      <c r="D69" s="235">
+        <v>120000</v>
+      </c>
+      <c r="E69" s="199" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="211" t="s">
+        <v>249</v>
+      </c>
+      <c r="B70" s="210"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="235">
+        <v>190500</v>
+      </c>
+      <c r="E70" s="199" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="209" t="s">
+        <v>243</v>
+      </c>
+      <c r="B71" s="210"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="183">
+        <v>240000</v>
+      </c>
+      <c r="E71" s="199" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="209" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="5" t="s">
+      <c r="B72" s="210"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="124">
+        <v>260000</v>
+      </c>
+      <c r="E72" s="191" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="166"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="184">
-        <v>120000</v>
-      </c>
-      <c r="E70" s="201" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="212" t="s">
-        <v>62</v>
-      </c>
-      <c r="B71" s="211"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="184">
-        <v>111908.93</v>
-      </c>
-      <c r="E71" s="194" t="s">
-        <v>63</v>
-      </c>
-      <c r="H71" s="167" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="210" t="s">
-        <v>254</v>
-      </c>
-      <c r="B72" s="211"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="184">
-        <v>240000</v>
-      </c>
-      <c r="E72" s="201" t="s">
-        <v>65</v>
-      </c>
-      <c r="H72" s="167" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="210" t="s">
-        <v>67</v>
-      </c>
-      <c r="B73" s="211"/>
+    </row>
+    <row r="73" spans="1:5" ht="52.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="209" t="s">
+        <v>244</v>
+      </c>
+      <c r="B73" s="210"/>
       <c r="C73" s="5"/>
       <c r="D73" s="124">
-        <v>260000</v>
-      </c>
-      <c r="E73" s="192" t="s">
-        <v>68</v>
-      </c>
-      <c r="H73" s="167"/>
-    </row>
-    <row r="74" spans="1:8" ht="52.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="210" t="s">
+        <v>240000</v>
+      </c>
+      <c r="E73" s="191" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="236" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" s="237"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="151">
+        <v>450000</v>
+      </c>
+      <c r="E74" s="191" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="209" t="s">
+        <v>256</v>
+      </c>
+      <c r="B75" s="210"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="151">
+        <v>85000</v>
+      </c>
+      <c r="E75" s="191" t="s">
         <v>255</v>
       </c>
-      <c r="B74" s="211"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="124">
-        <v>240000</v>
-      </c>
-      <c r="E74" s="192" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="210" t="s">
-        <v>69</v>
-      </c>
-      <c r="B75" s="211"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="124">
-        <v>45000</v>
-      </c>
-      <c r="E75" s="192" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="210" t="s">
-        <v>70</v>
-      </c>
-      <c r="B76" s="211"/>
+    </row>
+    <row r="76" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="209" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" s="210"/>
       <c r="C76" s="5"/>
       <c r="D76" s="124">
-        <v>130000</v>
-      </c>
-      <c r="E76" s="192" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="210" t="s">
-        <v>71</v>
-      </c>
-      <c r="B77" s="211"/>
+        <v>210000</v>
+      </c>
+      <c r="E76" s="191" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="209" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="210"/>
       <c r="C77" s="5"/>
       <c r="D77" s="124">
-        <v>210000</v>
-      </c>
-      <c r="E77" s="192" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="210" t="s">
-        <v>72</v>
-      </c>
-      <c r="B78" s="211"/>
+        <v>115000</v>
+      </c>
+      <c r="E77" s="191" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="209" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" s="210"/>
       <c r="C78" s="5"/>
       <c r="D78" s="124">
-        <v>115000</v>
-      </c>
-      <c r="E78" s="192" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="210" t="s">
-        <v>73</v>
-      </c>
-      <c r="B79" s="211"/>
+        <v>360000</v>
+      </c>
+      <c r="E78" s="191" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="204" t="s">
+        <v>66</v>
+      </c>
+      <c r="B79" s="197"/>
       <c r="C79" s="5"/>
       <c r="D79" s="124">
-        <v>360000</v>
-      </c>
-      <c r="E79" s="192" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="206" t="s">
-        <v>75</v>
-      </c>
-      <c r="B80" s="199"/>
+        <v>710000</v>
+      </c>
+      <c r="E79" s="191" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="58.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="209" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80" s="210"/>
       <c r="C80" s="5"/>
       <c r="D80" s="124">
-        <v>710000</v>
-      </c>
-      <c r="E80" s="192" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="58.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="210" t="s">
-        <v>77</v>
-      </c>
-      <c r="B81" s="211"/>
+        <v>770000</v>
+      </c>
+      <c r="E80" s="191" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="209" t="s">
+        <v>69</v>
+      </c>
+      <c r="B81" s="210"/>
       <c r="C81" s="5"/>
       <c r="D81" s="124">
-        <v>770000</v>
-      </c>
-      <c r="E81" s="192" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="210" t="s">
-        <v>78</v>
-      </c>
-      <c r="B82" s="211"/>
+        <v>120000</v>
+      </c>
+      <c r="E81" s="191" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="196" t="s">
+        <v>70</v>
+      </c>
+      <c r="B82" s="197"/>
       <c r="C82" s="5"/>
       <c r="D82" s="124">
-        <v>120000</v>
-      </c>
-      <c r="E82" s="192" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="198" t="s">
-        <v>79</v>
-      </c>
-      <c r="B83" s="199"/>
+        <v>12000</v>
+      </c>
+      <c r="E82" s="191" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="236"/>
+      <c r="B83" s="237"/>
       <c r="C83" s="5"/>
-      <c r="D83" s="124">
-        <v>12000</v>
-      </c>
-      <c r="E83" s="192" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="210" t="s">
-        <v>80</v>
-      </c>
-      <c r="B84" s="211"/>
+      <c r="D83" s="151">
+        <f>178500</f>
+        <v>178500</v>
+      </c>
+      <c r="E83" s="191" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="211"/>
+      <c r="B84" s="210"/>
       <c r="C84" s="5"/>
-      <c r="D84" s="124">
-        <f>1600+6400</f>
-        <v>8000</v>
-      </c>
-      <c r="E84" s="192"/>
-    </row>
-    <row r="85" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="212"/>
-      <c r="B85" s="211"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="124"/>
-      <c r="E85" s="195"/>
-      <c r="I85" s="212"/>
-      <c r="J85" s="211"/>
+      <c r="D84" s="124"/>
+      <c r="E84" s="193"/>
+      <c r="I84" s="211"/>
+      <c r="J84" s="210"/>
+    </row>
+    <row r="85" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B85" s="37"/>
+      <c r="C85" s="37"/>
+      <c r="D85" s="36"/>
+      <c r="E85" s="194">
+        <f>SUM(D65:D84)</f>
+        <v>4683000</v>
+      </c>
     </row>
     <row r="86" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="B86" s="37"/>
-      <c r="C86" s="37"/>
-      <c r="D86" s="36"/>
-      <c r="E86" s="196">
-        <f>SUM(D65:D85)</f>
-        <v>4124808.9299999997</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="B87" s="71"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="174"/>
-      <c r="E87" s="193"/>
+      <c r="A86" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B86" s="71"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="173"/>
+      <c r="E86" s="192"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="183">
+        <f>14894.24+10203+42365+10884.56+32649.71+17876.73+7400.53</f>
+        <v>136273.76999999999</v>
+      </c>
+      <c r="E87" s="195"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
-      <c r="D88" s="184">
-        <f>14894.24+10203+42365+10884.56+32649.71+17876.73+7400.53</f>
+      <c r="D88" s="183"/>
+      <c r="E88" s="126"/>
+    </row>
+    <row r="89" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" s="54"/>
+      <c r="C89" s="54"/>
+      <c r="D89" s="127"/>
+      <c r="E89" s="121">
+        <f>SUM(D87:D88)</f>
         <v>136273.76999999999</v>
       </c>
-      <c r="E88" s="197"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="184"/>
-      <c r="E89" s="126"/>
     </row>
     <row r="90" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="B90" s="54"/>
-      <c r="C90" s="54"/>
-      <c r="D90" s="127"/>
-      <c r="E90" s="121">
-        <f>SUM(D88:D89)</f>
-        <v>136273.76999999999</v>
-      </c>
+      <c r="A90" s="5"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="120"/>
+      <c r="E90" s="128"/>
     </row>
     <row r="91" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="120"/>
-      <c r="E91" s="128"/>
+      <c r="A91" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B91" s="32"/>
+      <c r="C91" s="32"/>
+      <c r="D91" s="129"/>
+      <c r="E91" s="130"/>
     </row>
     <row r="92" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="B92" s="32"/>
-      <c r="C92" s="32"/>
-      <c r="D92" s="129"/>
-      <c r="E92" s="130"/>
+      <c r="A92" s="1"/>
+      <c r="D92" s="131"/>
+      <c r="E92" s="132"/>
+      <c r="F92" s="46"/>
     </row>
     <row r="93" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
-      <c r="D93" s="131"/>
-      <c r="E93" s="132"/>
-      <c r="F93" s="46"/>
-    </row>
-    <row r="94" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B94" s="10"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="133"/>
-      <c r="E94" s="134">
-        <f>(SUM(E31:E92))</f>
-        <v>12841476.049999999</v>
-      </c>
-      <c r="F94" s="162"/>
-      <c r="G94" s="46"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B93" s="10"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="133"/>
+      <c r="E93" s="134">
+        <f>(SUM(E31:E91))</f>
+        <v>13476319.09</v>
+      </c>
+      <c r="F93" s="162"/>
+      <c r="G93" s="46"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D94" s="131"/>
+      <c r="E94" s="131"/>
+    </row>
+    <row r="95" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D95" s="131"/>
       <c r="E95" s="131"/>
     </row>
-    <row r="96" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D96" s="131"/>
-      <c r="E96" s="131"/>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B96" s="12"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="135"/>
+      <c r="E96" s="136"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B97" s="12"/>
-      <c r="C97" s="13"/>
-      <c r="D97" s="135"/>
-      <c r="E97" s="136"/>
+      <c r="A97" s="211"/>
+      <c r="B97" s="210"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="151"/>
+      <c r="E97" s="122"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="212"/>
-      <c r="B98" s="211"/>
+      <c r="A98" s="211"/>
+      <c r="B98" s="210"/>
       <c r="C98" s="5"/>
-      <c r="D98" s="151"/>
+      <c r="D98" s="124"/>
       <c r="E98" s="122"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="212"/>
-      <c r="B99" s="211"/>
+    <row r="99" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="209"/>
+      <c r="B99" s="210"/>
       <c r="C99" s="5"/>
       <c r="D99" s="124"/>
       <c r="E99" s="122"/>
     </row>
-    <row r="100" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="210"/>
-      <c r="B100" s="211"/>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="123"/>
+      <c r="B100" s="125"/>
       <c r="C100" s="5"/>
       <c r="D100" s="124"/>
       <c r="E100" s="122"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="123"/>
-      <c r="B101" s="125"/>
-      <c r="C101" s="5"/>
-      <c r="D101" s="124"/>
-      <c r="E101" s="122"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="52"/>
-      <c r="B102" s="51"/>
-      <c r="C102" s="51"/>
-      <c r="D102" s="61"/>
-      <c r="E102" s="61">
-        <f>SUM(D98:D101)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="105" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="B105" s="32"/>
-      <c r="C105" s="32"/>
-      <c r="D105" s="33"/>
-      <c r="E105" s="119"/>
-    </row>
-    <row r="106" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="107" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B107" s="10"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="72">
-        <f>E102+E105</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="A101" s="52"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="61"/>
+      <c r="E101" s="61">
+        <f>SUM(D97:D100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="1:5" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="B104" s="32"/>
+      <c r="C104" s="32"/>
+      <c r="D104" s="33"/>
+      <c r="E104" s="119"/>
+    </row>
+    <row r="105" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="106" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B106" s="10"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="72">
+        <f>E101+E104</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="116" t="s">
+        <v>79</v>
+      </c>
+      <c r="B108" s="117">
+        <f>E93</f>
+        <v>13476319.09</v>
+      </c>
+    </row>
     <row r="109" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="116" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B109" s="117">
-        <f>E94</f>
-        <v>12841476.049999999</v>
+        <f>E93-E91</f>
+        <v>13476319.09</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="116" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B110" s="117">
-        <f>E94-E92</f>
-        <v>12841476.049999999</v>
+        <f>E106-E104</f>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="116" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B111" s="117">
-        <f>E107-E105</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="116" t="s">
-        <v>92</v>
-      </c>
-      <c r="B112" s="117">
-        <f>E107</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="73.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="216" t="s">
-        <v>93</v>
-      </c>
-      <c r="B113" s="217"/>
-    </row>
-    <row r="114" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="220"/>
-      <c r="B115" s="214"/>
-      <c r="C115" s="214"/>
-      <c r="D115" s="214"/>
-      <c r="E115" s="214"/>
-    </row>
-    <row r="116" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="214"/>
-      <c r="B116" s="214"/>
-      <c r="C116" s="214"/>
-      <c r="D116" s="214"/>
-      <c r="E116" s="214"/>
-    </row>
-    <row r="117" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="214"/>
-      <c r="B117" s="214"/>
-      <c r="C117" s="214"/>
-      <c r="D117" s="214"/>
-      <c r="E117" s="214"/>
-    </row>
-    <row r="119" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B119" s="147"/>
-      <c r="C119" s="24"/>
-    </row>
-    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="35"/>
-      <c r="B120" s="62">
-        <v>0</v>
-      </c>
-      <c r="C120" s="26"/>
-    </row>
-    <row r="121" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="B121" s="42">
+        <f>E106</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="73.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="216" t="s">
+        <v>83</v>
+      </c>
+      <c r="B112" s="217"/>
+    </row>
+    <row r="113" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="213"/>
+      <c r="B114" s="208"/>
+      <c r="C114" s="208"/>
+      <c r="D114" s="208"/>
+      <c r="E114" s="208"/>
+    </row>
+    <row r="115" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="208"/>
+      <c r="B115" s="208"/>
+      <c r="C115" s="208"/>
+      <c r="D115" s="208"/>
+      <c r="E115" s="208"/>
+    </row>
+    <row r="116" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="208"/>
+      <c r="B116" s="208"/>
+      <c r="C116" s="208"/>
+      <c r="D116" s="208"/>
+      <c r="E116" s="208"/>
+    </row>
+    <row r="118" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B118" s="147"/>
+      <c r="C118" s="24"/>
+    </row>
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="35"/>
+      <c r="B119" s="62">
+        <v>0</v>
+      </c>
+      <c r="C119" s="26"/>
+    </row>
+    <row r="120" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B120" s="42">
         <f>PRORRATEO!I81</f>
         <v>10964795.799999999</v>
       </c>
+      <c r="C120" s="24"/>
+    </row>
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="25"/>
+      <c r="B121" s="42">
+        <v>0</v>
+      </c>
       <c r="C121" s="24"/>
     </row>
-    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="25"/>
-      <c r="B122" s="42">
-        <v>0</v>
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B122" s="126">
+        <f>B145</f>
+        <v>184089</v>
       </c>
       <c r="C122" s="24"/>
     </row>
-    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="B123" s="126">
-        <f>B146</f>
-        <v>184089</v>
-      </c>
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="28"/>
+      <c r="B123" s="50"/>
       <c r="C123" s="24"/>
     </row>
-    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="28"/>
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="141" t="s">
+        <v>87</v>
+      </c>
       <c r="B124" s="50"/>
       <c r="C124" s="24"/>
     </row>
-    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="141" t="s">
-        <v>97</v>
-      </c>
-      <c r="B125" s="50"/>
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="B125" s="50">
+        <f>-B109</f>
+        <v>-13476319.09</v>
+      </c>
       <c r="C125" s="24"/>
     </row>
-    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="41" t="s">
-        <v>98</v>
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="28" t="s">
+        <v>89</v>
       </c>
       <c r="B126" s="50">
-        <f>-B110</f>
-        <v>-12841476.049999999</v>
+        <f>-(B110)</f>
+        <v>0</v>
       </c>
       <c r="C126" s="24"/>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="B127" s="50">
-        <f>-(B111)</f>
-        <v>0</v>
-      </c>
-      <c r="C127" s="24"/>
-    </row>
-    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="B128" s="62">
-        <f>SUM(B120:B127)</f>
-        <v>-1692591.25</v>
-      </c>
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B127" s="62">
+        <f>SUM(B119:B126)</f>
+        <v>-2327434.290000001</v>
+      </c>
+      <c r="C127" s="27"/>
+      <c r="D127" s="46"/>
+    </row>
+    <row r="128" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B128" s="43"/>
       <c r="C128" s="27"/>
       <c r="D128" s="46"/>
-    </row>
-    <row r="129" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="43"/>
+      <c r="E128" s="148"/>
+      <c r="F128" s="149"/>
+    </row>
+    <row r="129" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B129" s="44"/>
       <c r="C129" s="27"/>
-      <c r="D129" s="46"/>
-      <c r="E129" s="148"/>
-      <c r="F129" s="149"/>
-    </row>
-    <row r="130" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="44"/>
-      <c r="C130" s="27"/>
-    </row>
-    <row r="131" spans="1:6" s="40" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="43"/>
+    </row>
+    <row r="130" spans="1:4" s="40" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B130" s="43"/>
+      <c r="C130" s="39"/>
+    </row>
+    <row r="131" spans="1:4" s="40" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="153" t="s">
+        <v>90</v>
+      </c>
+      <c r="B131" s="154">
+        <v>1422704.1999999939</v>
+      </c>
       <c r="C131" s="39"/>
-    </row>
-    <row r="132" spans="1:6" s="40" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="153" t="s">
-        <v>100</v>
-      </c>
-      <c r="B132" s="154">
-        <v>1422704.1999999939</v>
-      </c>
-      <c r="C132" s="39"/>
-      <c r="D132" s="49"/>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D131" s="49"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="B132" s="158">
+        <f>-B109</f>
+        <v>-13476319.09</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="57" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B133" s="158">
         <f>-B110</f>
-        <v>-12841476.049999999</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="57" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B134" s="158">
-        <f>-B111</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+        <f>B145</f>
+        <v>184089</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="57" t="s">
-        <v>103</v>
-      </c>
-      <c r="B135" s="158">
-        <f>B146</f>
-        <v>184089</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" s="57" t="s">
-        <v>104</v>
-      </c>
-      <c r="B136" s="159">
+        <v>94</v>
+      </c>
+      <c r="B135" s="159">
         <f>PRORRATEO!I81</f>
         <v>10964795.799999999</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="B137" s="204">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="B136" s="202">
         <v>-65000</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" s="160" t="s">
-        <v>106</v>
-      </c>
-      <c r="B138" s="161"/>
-    </row>
-    <row r="139" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="156" t="s">
-        <v>107</v>
-      </c>
-      <c r="B139" s="157">
-        <f>SUM(B132:C138)</f>
-        <v>-334887.05000000633</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" s="155"/>
-      <c r="B140" s="155"/>
-    </row>
-    <row r="141" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" s="213" t="s">
-        <v>108</v>
-      </c>
-      <c r="B142" s="214"/>
-      <c r="C142" s="214"/>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" s="214"/>
-      <c r="B143" s="214"/>
-      <c r="C143" s="214"/>
-    </row>
-    <row r="144" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="138" t="s">
-        <v>109</v>
-      </c>
-      <c r="B144" s="38">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="160" t="s">
+        <v>96</v>
+      </c>
+      <c r="B137" s="161"/>
+    </row>
+    <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="156" t="s">
+        <v>97</v>
+      </c>
+      <c r="B138" s="157">
+        <f>SUM(B131:C137)</f>
+        <v>-969730.0900000073</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="155"/>
+      <c r="B139" s="155"/>
+    </row>
+    <row r="140" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="218" t="s">
+        <v>98</v>
+      </c>
+      <c r="B141" s="208"/>
+      <c r="C141" s="208"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="208"/>
+      <c r="B142" s="208"/>
+      <c r="C142" s="208"/>
+    </row>
+    <row r="143" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="138" t="s">
+        <v>99</v>
+      </c>
+      <c r="B143" s="38">
         <v>184089</v>
       </c>
-      <c r="C144" s="38">
+      <c r="C143" s="38">
         <v>40000</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="138"/>
-      <c r="B145" s="140"/>
-      <c r="C145" s="43"/>
+    <row r="144" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="138"/>
+      <c r="B144" s="140"/>
+      <c r="C144" s="43"/>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="B145" s="139">
+        <f>SUM(B143:B144)</f>
+        <v>184089</v>
+      </c>
+      <c r="C145" s="48"/>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A146" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="B146" s="139">
-        <f>SUM(B144:B145)</f>
-        <v>184089</v>
-      </c>
-      <c r="C146" s="48"/>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M147" s="8"/>
-    </row>
-    <row r="148" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="220"/>
-      <c r="B148" s="214"/>
-      <c r="C148" s="214"/>
-      <c r="D148" s="214"/>
-      <c r="E148" s="214"/>
+      <c r="M146" s="8"/>
+    </row>
+    <row r="147" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="213"/>
+      <c r="B147" s="208"/>
+      <c r="C147" s="208"/>
+      <c r="D147" s="208"/>
+      <c r="E147" s="208"/>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" s="208"/>
+      <c r="B148" s="208"/>
+      <c r="C148" s="208"/>
+      <c r="D148" s="208"/>
+      <c r="E148" s="208"/>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A149" s="214"/>
-      <c r="B149" s="214"/>
-      <c r="C149" s="214"/>
-      <c r="D149" s="214"/>
-      <c r="E149" s="214"/>
+      <c r="A149" s="208"/>
+      <c r="B149" s="208"/>
+      <c r="C149" s="208"/>
+      <c r="D149" s="208"/>
+      <c r="E149" s="208"/>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A150" s="214"/>
-      <c r="B150" s="214"/>
-      <c r="C150" s="214"/>
-      <c r="D150" s="214"/>
-      <c r="E150" s="214"/>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A151" s="214"/>
-      <c r="B151" s="214"/>
-      <c r="C151" s="214"/>
-      <c r="D151" s="214"/>
-      <c r="E151" s="214"/>
+      <c r="A150" s="208"/>
+      <c r="B150" s="208"/>
+      <c r="C150" s="208"/>
+      <c r="D150" s="208"/>
+      <c r="E150" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A141:C142"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A112:B112"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="A65:B65"/>
     <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A84:B84"/>
     <mergeCell ref="D62:E62"/>
-    <mergeCell ref="A148:E151"/>
-    <mergeCell ref="A115:E117"/>
-    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A147:E150"/>
+    <mergeCell ref="A114:E116"/>
+    <mergeCell ref="A99:B99"/>
     <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A80:B80"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A76:B76"/>
     <mergeCell ref="A14:E17"/>
     <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A142:C143"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A78:B78"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3673,16 +3664,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="228"/>
-      <c r="H1" s="214"/>
-      <c r="I1" s="214"/>
-      <c r="J1" s="214"/>
-      <c r="K1" s="214"/>
-      <c r="L1" s="214"/>
-      <c r="M1" s="214"/>
-      <c r="N1" s="214"/>
-      <c r="O1" s="214"/>
-      <c r="P1" s="214"/>
+      <c r="G1" s="232"/>
+      <c r="H1" s="208"/>
+      <c r="I1" s="208"/>
+      <c r="J1" s="208"/>
+      <c r="K1" s="208"/>
+      <c r="L1" s="208"/>
+      <c r="M1" s="208"/>
+      <c r="N1" s="208"/>
+      <c r="O1" s="208"/>
+      <c r="P1" s="208"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -3702,16 +3693,16 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="224">
+      <c r="P2" s="229">
         <v>12376831.439999999</v>
       </c>
-      <c r="Q2" s="214"/>
-      <c r="R2" s="214"/>
+      <c r="Q2" s="208"/>
+      <c r="R2" s="208"/>
       <c r="S2" s="22"/>
     </row>
     <row r="3" spans="1:21" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3735,96 +3726,96 @@
       <c r="R3" s="63"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="234" t="s">
+      <c r="A4" s="224" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="226" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="142"/>
+      <c r="D4" s="219" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="219" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="221" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="219" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="223" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="219" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" s="221" t="s">
+        <v>108</v>
+      </c>
+      <c r="K4" s="225" t="s">
+        <v>109</v>
+      </c>
+      <c r="L4" s="223" t="s">
+        <v>110</v>
+      </c>
+      <c r="M4" s="234" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="237" t="s">
+      <c r="N4" s="223" t="s">
         <v>112</v>
       </c>
-      <c r="C4" s="142"/>
-      <c r="D4" s="225" t="s">
+      <c r="O4" s="230" t="s">
         <v>113</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="P4" s="66" t="s">
         <v>114</v>
       </c>
-      <c r="F4" s="231" t="s">
+      <c r="Q4" s="233" t="s">
         <v>115</v>
       </c>
-      <c r="G4" s="225" t="s">
+      <c r="R4" s="228" t="s">
         <v>116</v>
       </c>
-      <c r="H4" s="233" t="s">
-        <v>117</v>
-      </c>
-      <c r="I4" s="225" t="s">
-        <v>95</v>
-      </c>
-      <c r="J4" s="231" t="s">
-        <v>118</v>
-      </c>
-      <c r="K4" s="235" t="s">
-        <v>119</v>
-      </c>
-      <c r="L4" s="233" t="s">
-        <v>120</v>
-      </c>
-      <c r="M4" s="236" t="s">
-        <v>121</v>
-      </c>
-      <c r="N4" s="233" t="s">
-        <v>122</v>
-      </c>
-      <c r="O4" s="226" t="s">
-        <v>123</v>
-      </c>
-      <c r="P4" s="66" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q4" s="229" t="s">
-        <v>125</v>
-      </c>
-      <c r="R4" s="222" t="s">
-        <v>126</v>
-      </c>
       <c r="U4" s="46"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="223"/>
-      <c r="B5" s="230"/>
+      <c r="A5" s="220"/>
+      <c r="B5" s="227"/>
       <c r="C5" s="143"/>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="232"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="232"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="232"/>
-      <c r="K5" s="232"/>
-      <c r="L5" s="232"/>
-      <c r="M5" s="223"/>
-      <c r="N5" s="232"/>
-      <c r="O5" s="227"/>
+      <c r="D5" s="220"/>
+      <c r="E5" s="220"/>
+      <c r="F5" s="222"/>
+      <c r="G5" s="220"/>
+      <c r="H5" s="222"/>
+      <c r="I5" s="220"/>
+      <c r="J5" s="222"/>
+      <c r="K5" s="222"/>
+      <c r="L5" s="222"/>
+      <c r="M5" s="220"/>
+      <c r="N5" s="222"/>
+      <c r="O5" s="231"/>
       <c r="P5" s="64" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/07</v>
       </c>
-      <c r="Q5" s="230"/>
-      <c r="R5" s="223"/>
+      <c r="Q5" s="227"/>
+      <c r="R5" s="220"/>
     </row>
     <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B6" s="68"/>
       <c r="C6" s="68" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D6" s="68">
         <v>1</v>
       </c>
       <c r="E6" s="68" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F6" s="68"/>
       <c r="G6" s="77">
@@ -3833,7 +3824,7 @@
       <c r="H6" s="78">
         <v>58374.01</v>
       </c>
-      <c r="I6" s="168">
+      <c r="I6" s="167">
         <f>722774-I13-I7-I47-I48-I59-I69-I73</f>
         <v>58374.190000000061</v>
       </c>
@@ -3872,23 +3863,23 @@
         <v>0.01</v>
       </c>
       <c r="U6" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B7" s="68"/>
       <c r="C7" s="68" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D7" s="68">
         <f t="shared" ref="D7:D38" si="6">D6+1</f>
         <v>2</v>
       </c>
       <c r="E7" s="68" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F7" s="69"/>
       <c r="G7" s="77">
@@ -3897,7 +3888,7 @@
       <c r="H7" s="78">
         <v>69615.02</v>
       </c>
-      <c r="I7" s="168">
+      <c r="I7" s="167">
         <f>H7</f>
         <v>69615.02</v>
       </c>
@@ -3940,7 +3931,7 @@
     </row>
     <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B8" s="68">
         <v>1</v>
@@ -3951,7 +3942,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="68" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F8" s="69"/>
       <c r="G8" s="77">
@@ -3960,7 +3951,7 @@
       <c r="H8" s="78">
         <v>69569.03</v>
       </c>
-      <c r="I8" s="168"/>
+      <c r="I8" s="167"/>
       <c r="J8" s="80"/>
       <c r="K8" s="81">
         <f t="shared" si="0"/>
@@ -3999,7 +3990,7 @@
     </row>
     <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B9" s="68">
         <v>2</v>
@@ -4010,7 +4001,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="68" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F9" s="69"/>
       <c r="G9" s="77">
@@ -4019,7 +4010,7 @@
       <c r="H9" s="78">
         <v>57260.04</v>
       </c>
-      <c r="I9" s="168"/>
+      <c r="I9" s="167"/>
       <c r="J9" s="80"/>
       <c r="K9" s="81">
         <f t="shared" si="0"/>
@@ -4059,7 +4050,7 @@
     </row>
     <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B10" s="68">
         <v>3</v>
@@ -4070,7 +4061,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="68" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F10" s="69"/>
       <c r="G10" s="77">
@@ -4079,7 +4070,7 @@
       <c r="H10" s="78">
         <v>57260.05</v>
       </c>
-      <c r="I10" s="168"/>
+      <c r="I10" s="167"/>
       <c r="J10" s="80"/>
       <c r="K10" s="81">
         <f t="shared" si="0"/>
@@ -4119,7 +4110,7 @@
     </row>
     <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B11" s="68">
         <v>4</v>
@@ -4130,10 +4121,10 @@
         <v>6</v>
       </c>
       <c r="E11" s="68" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F11" s="68" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="G11" s="77">
         <v>0.74990000000000001</v>
@@ -4141,7 +4132,7 @@
       <c r="H11" s="78">
         <v>85315.06</v>
       </c>
-      <c r="I11" s="168">
+      <c r="I11" s="167">
         <f>H11</f>
         <v>85315.06</v>
       </c>
@@ -4183,7 +4174,7 @@
     </row>
     <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B12" s="68">
         <v>5</v>
@@ -4194,10 +4185,10 @@
         <v>7</v>
       </c>
       <c r="E12" s="68" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F12" s="68" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="G12" s="77">
         <v>0.54249999999999998</v>
@@ -4205,7 +4196,7 @@
       <c r="H12" s="78">
         <v>61719.07</v>
       </c>
-      <c r="I12" s="168">
+      <c r="I12" s="167">
         <f>H12</f>
         <v>61719.07</v>
       </c>
@@ -4247,7 +4238,7 @@
     </row>
     <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B13" s="68">
         <v>6</v>
@@ -4258,7 +4249,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="68" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F13" s="69"/>
       <c r="G13" s="77">
@@ -4267,7 +4258,7 @@
       <c r="H13" s="78">
         <v>51617.08</v>
       </c>
-      <c r="I13" s="168">
+      <c r="I13" s="167">
         <f>H13</f>
         <v>51617.08</v>
       </c>
@@ -4309,7 +4300,7 @@
     </row>
     <row r="14" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B14" s="68">
         <v>7</v>
@@ -4320,10 +4311,10 @@
         <v>9</v>
       </c>
       <c r="E14" s="68" t="s">
-        <v>142</v>
-      </c>
-      <c r="F14" s="208" t="s">
-        <v>143</v>
+        <v>132</v>
+      </c>
+      <c r="F14" s="205" t="s">
+        <v>133</v>
       </c>
       <c r="G14" s="77">
         <v>0.52439999999999998</v>
@@ -4331,7 +4322,7 @@
       <c r="H14" s="78">
         <v>117417.09</v>
       </c>
-      <c r="I14" s="168">
+      <c r="I14" s="167">
         <f>H14-59660</f>
         <v>57757.09</v>
       </c>
@@ -4371,12 +4362,12 @@
         <v>0.09</v>
       </c>
       <c r="U14" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B15" s="68">
         <v>8</v>
@@ -4387,10 +4378,10 @@
         <v>10</v>
       </c>
       <c r="E15" s="68" t="s">
-        <v>142</v>
-      </c>
-      <c r="F15" s="208" t="s">
-        <v>143</v>
+        <v>132</v>
+      </c>
+      <c r="F15" s="205" t="s">
+        <v>133</v>
       </c>
       <c r="G15" s="77">
         <v>0.42399999999999999</v>
@@ -4398,7 +4389,7 @@
       <c r="H15" s="78">
         <v>48238.1</v>
       </c>
-      <c r="I15" s="168"/>
+      <c r="I15" s="167"/>
       <c r="J15" s="80"/>
       <c r="K15" s="81">
         <f t="shared" si="0"/>
@@ -4435,25 +4426,25 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="U15" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B16" s="68">
         <v>1</v>
       </c>
       <c r="C16" s="68" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D16" s="68">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="E16" s="68" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="F16" s="69"/>
       <c r="G16" s="77">
@@ -4462,7 +4453,7 @@
       <c r="H16" s="78">
         <v>2885042.11</v>
       </c>
-      <c r="I16" s="168"/>
+      <c r="I16" s="167"/>
       <c r="J16" s="80"/>
       <c r="K16" s="81">
         <f t="shared" si="0"/>
@@ -4501,23 +4492,23 @@
     </row>
     <row r="17" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B17" s="68">
         <v>1</v>
       </c>
       <c r="C17" s="68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D17" s="68">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="E17" s="68" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F17" s="69" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G17" s="77">
         <v>2.7492999999999999</v>
@@ -4525,7 +4516,7 @@
       <c r="H17" s="78">
         <v>322166</v>
       </c>
-      <c r="I17" s="168">
+      <c r="I17" s="167">
         <f>H17</f>
         <v>322166</v>
       </c>
@@ -4567,23 +4558,23 @@
     </row>
     <row r="18" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B18" s="68">
         <v>2</v>
       </c>
       <c r="C18" s="68" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D18" s="68">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="E18" s="68" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="F18" s="69" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="G18" s="77">
         <v>2.3033000000000001</v>
@@ -4591,7 +4582,7 @@
       <c r="H18" s="78">
         <v>262043.13</v>
       </c>
-      <c r="I18" s="168">
+      <c r="I18" s="167">
         <f>H18</f>
         <v>262043.13</v>
       </c>
@@ -4633,23 +4624,23 @@
     </row>
     <row r="19" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B19" s="68">
         <v>2</v>
       </c>
       <c r="C19" s="68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D19" s="68">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="E19" s="68" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="F19" s="69" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="G19" s="77">
         <v>2.6368</v>
@@ -4657,7 +4648,7 @@
       <c r="H19" s="78">
         <v>567768.14</v>
       </c>
-      <c r="I19" s="168">
+      <c r="I19" s="167">
         <f>40000+528000</f>
         <v>568000</v>
       </c>
@@ -4697,25 +4688,25 @@
         <v>0.13999999999999999</v>
       </c>
       <c r="U19" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B20" s="68">
         <v>3</v>
       </c>
       <c r="C20" s="68" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D20" s="68">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="E20" s="68" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="F20" s="69"/>
       <c r="G20" s="77">
@@ -4724,7 +4715,7 @@
       <c r="H20" s="78">
         <v>267776.15000000002</v>
       </c>
-      <c r="I20" s="168">
+      <c r="I20" s="167">
         <f>H20</f>
         <v>267776.15000000002</v>
       </c>
@@ -4766,23 +4757,23 @@
     </row>
     <row r="21" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B21" s="68">
         <v>3</v>
       </c>
       <c r="C21" s="68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D21" s="68">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="E21" s="68" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F21" s="68" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="G21" s="77">
         <v>2.6476999999999999</v>
@@ -4790,7 +4781,7 @@
       <c r="H21" s="78">
         <v>301224.15999999997</v>
       </c>
-      <c r="I21" s="168">
+      <c r="I21" s="167">
         <f>H21</f>
         <v>301224.15999999997</v>
       </c>
@@ -4833,23 +4824,23 @@
     </row>
     <row r="22" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B22" s="68">
         <v>4</v>
       </c>
       <c r="C22" s="68" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D22" s="68">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="E22" s="68" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="F22" s="69" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="G22" s="77">
         <v>2.3235000000000001</v>
@@ -4857,7 +4848,7 @@
       <c r="H22" s="79">
         <v>264341.17</v>
       </c>
-      <c r="I22" s="168">
+      <c r="I22" s="167">
         <f>H22</f>
         <v>264341.17</v>
       </c>
@@ -4899,23 +4890,23 @@
     </row>
     <row r="23" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B23" s="68">
         <v>4</v>
       </c>
       <c r="C23" s="68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D23" s="68">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="E23" s="68" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="F23" s="152" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="G23" s="77">
         <v>2.6880000000000002</v>
@@ -4923,7 +4914,7 @@
       <c r="H23" s="78">
         <v>291809.18</v>
       </c>
-      <c r="I23" s="168">
+      <c r="I23" s="167">
         <v>300500</v>
       </c>
       <c r="J23" s="80"/>
@@ -4962,25 +4953,25 @@
         <v>0.18000000000000002</v>
       </c>
       <c r="U23" s="163" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B24" s="68">
         <v>5</v>
       </c>
       <c r="C24" s="68" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D24" s="68">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="E24" s="68" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F24" s="69"/>
       <c r="G24" s="77">
@@ -4989,7 +4980,7 @@
       <c r="H24" s="78">
         <v>268493.19</v>
       </c>
-      <c r="I24" s="168">
+      <c r="I24" s="167">
         <f>H24</f>
         <v>268493.19</v>
       </c>
@@ -5031,20 +5022,20 @@
     </row>
     <row r="25" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B25" s="68">
         <v>5</v>
       </c>
       <c r="C25" s="68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D25" s="68">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="E25" s="68" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="F25" s="68"/>
       <c r="G25" s="77">
@@ -5053,7 +5044,7 @@
       <c r="H25" s="78">
         <v>307735.2</v>
       </c>
-      <c r="I25" s="168">
+      <c r="I25" s="167">
         <v>317000</v>
       </c>
       <c r="J25" s="80"/>
@@ -5094,20 +5085,20 @@
     </row>
     <row r="26" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B26" s="68">
         <v>6</v>
       </c>
       <c r="C26" s="68" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D26" s="68">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="E26" s="68" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="F26" s="69"/>
       <c r="G26" s="77">
@@ -5116,7 +5107,7 @@
       <c r="H26" s="78">
         <v>262043.21</v>
       </c>
-      <c r="I26" s="168">
+      <c r="I26" s="167">
         <f>H26</f>
         <v>262043.21</v>
       </c>
@@ -5158,23 +5149,23 @@
     </row>
     <row r="27" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B27" s="68">
         <v>6</v>
       </c>
       <c r="C27" s="68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D27" s="68">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="E27" s="68" t="s">
-        <v>173</v>
-      </c>
-      <c r="F27" s="208" t="s">
-        <v>174</v>
+        <v>163</v>
+      </c>
+      <c r="F27" s="205" t="s">
+        <v>164</v>
       </c>
       <c r="G27" s="77">
         <v>2.6360000000000001</v>
@@ -5182,7 +5173,7 @@
       <c r="H27" s="78">
         <v>772239.22</v>
       </c>
-      <c r="I27" s="168">
+      <c r="I27" s="167">
         <f>H27-454893</f>
         <v>317346.21999999997</v>
       </c>
@@ -5202,7 +5193,7 @@
         <f t="shared" si="2"/>
         <v>326253.27675840002</v>
       </c>
-      <c r="O27" s="205">
+      <c r="O27" s="203">
         <v>65000</v>
       </c>
       <c r="P27" s="85">
@@ -5222,28 +5213,28 @@
         <v>0.22000000000000006</v>
       </c>
       <c r="T27" s="69" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="U27" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="B28" s="68">
         <v>7</v>
       </c>
       <c r="C28" s="68" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D28" s="68">
         <f t="shared" si="6"/>
         <v>23</v>
       </c>
       <c r="E28" s="68" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="F28" s="69"/>
       <c r="G28" s="77">
@@ -5252,7 +5243,7 @@
       <c r="H28" s="78">
         <v>262043.23</v>
       </c>
-      <c r="I28" s="168">
+      <c r="I28" s="167">
         <f t="shared" ref="I28:I34" si="8">H28</f>
         <v>262043.23</v>
       </c>
@@ -5294,20 +5285,20 @@
     </row>
     <row r="29" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B29" s="68">
         <v>7</v>
       </c>
       <c r="C29" s="68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D29" s="68">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="E29" s="68" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="F29" s="69"/>
       <c r="G29" s="77">
@@ -5316,7 +5307,7 @@
       <c r="H29" s="78">
         <v>297607.24</v>
       </c>
-      <c r="I29" s="168">
+      <c r="I29" s="167">
         <f t="shared" si="8"/>
         <v>297607.24</v>
       </c>
@@ -5358,20 +5349,20 @@
     </row>
     <row r="30" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B30" s="68">
         <v>8</v>
       </c>
       <c r="C30" s="68" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D30" s="68">
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
       <c r="E30" s="68" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="F30" s="68"/>
       <c r="G30" s="77">
@@ -5380,7 +5371,7 @@
       <c r="H30" s="78">
         <v>267776.25</v>
       </c>
-      <c r="I30" s="168">
+      <c r="I30" s="167">
         <f t="shared" si="8"/>
         <v>267776.25</v>
       </c>
@@ -5422,23 +5413,23 @@
     </row>
     <row r="31" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B31" s="68">
         <v>8</v>
       </c>
       <c r="C31" s="68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D31" s="68">
         <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="E31" s="68" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="F31" s="68" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="G31" s="77">
         <v>2.6469</v>
@@ -5446,7 +5437,7 @@
       <c r="H31" s="78">
         <v>301133.26</v>
       </c>
-      <c r="I31" s="168">
+      <c r="I31" s="167">
         <f t="shared" si="8"/>
         <v>301133.26</v>
       </c>
@@ -5488,20 +5479,20 @@
     </row>
     <row r="32" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B32" s="68">
         <v>9</v>
       </c>
       <c r="C32" s="68" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D32" s="68">
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
       <c r="E32" s="68" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F32" s="69"/>
       <c r="G32" s="77">
@@ -5510,7 +5501,7 @@
       <c r="H32" s="78">
         <v>267776.27</v>
       </c>
-      <c r="I32" s="168">
+      <c r="I32" s="167">
         <f t="shared" si="8"/>
         <v>267776.27</v>
       </c>
@@ -5552,20 +5543,20 @@
     </row>
     <row r="33" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B33" s="68">
         <v>9</v>
       </c>
       <c r="C33" s="68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D33" s="68">
         <f t="shared" si="6"/>
         <v>28</v>
       </c>
       <c r="E33" s="68" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F33" s="68"/>
       <c r="G33" s="77">
@@ -5574,7 +5565,7 @@
       <c r="H33" s="78">
         <v>303340.28000000003</v>
       </c>
-      <c r="I33" s="168">
+      <c r="I33" s="167">
         <f t="shared" si="8"/>
         <v>303340.28000000003</v>
       </c>
@@ -5616,23 +5607,23 @@
     </row>
     <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B34" s="68">
         <v>10</v>
       </c>
       <c r="C34" s="68" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D34" s="68">
         <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="E34" s="68" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="F34" s="68" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="G34" s="77">
         <v>2.4476</v>
@@ -5640,7 +5631,7 @@
       <c r="H34" s="78">
         <v>278459.28999999998</v>
       </c>
-      <c r="I34" s="168">
+      <c r="I34" s="167">
         <f t="shared" si="8"/>
         <v>278459.28999999998</v>
       </c>
@@ -5682,20 +5673,20 @@
     </row>
     <row r="35" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B35" s="68">
         <v>10</v>
       </c>
       <c r="C35" s="68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D35" s="68">
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="E35" s="68" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="F35" s="69"/>
       <c r="G35" s="77">
@@ -5704,7 +5695,7 @@
       <c r="H35" s="78">
         <v>300521.3</v>
       </c>
-      <c r="I35" s="168"/>
+      <c r="I35" s="167"/>
       <c r="J35" s="80"/>
       <c r="K35" s="81">
         <f t="shared" si="0"/>
@@ -5743,23 +5734,23 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B36" s="68">
         <v>11</v>
       </c>
       <c r="C36" s="68" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D36" s="68">
         <f t="shared" si="6"/>
         <v>31</v>
       </c>
       <c r="E36" s="68" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="F36" s="68" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="G36" s="77">
         <v>2.3026</v>
@@ -5767,7 +5758,7 @@
       <c r="H36" s="79">
         <v>293522.31</v>
       </c>
-      <c r="I36" s="168">
+      <c r="I36" s="167">
         <f>H36</f>
         <v>293522.31</v>
       </c>
@@ -5809,20 +5800,20 @@
     </row>
     <row r="37" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B37" s="68">
         <v>11</v>
       </c>
       <c r="C37" s="68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D37" s="68">
         <f t="shared" si="6"/>
         <v>32</v>
       </c>
       <c r="E37" s="68" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F37" s="69"/>
       <c r="G37" s="77">
@@ -5831,7 +5822,7 @@
       <c r="H37" s="78">
         <v>422143.32</v>
       </c>
-      <c r="I37" s="168">
+      <c r="I37" s="167">
         <v>302191.32</v>
       </c>
       <c r="J37" s="80"/>
@@ -5872,20 +5863,20 @@
     </row>
     <row r="38" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B38" s="68">
         <v>12</v>
       </c>
       <c r="C38" s="68" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D38" s="68">
         <f t="shared" si="6"/>
         <v>33</v>
       </c>
       <c r="E38" s="68" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="F38" s="69"/>
       <c r="G38" s="77">
@@ -5894,7 +5885,7 @@
       <c r="H38" s="78">
         <v>265569.33</v>
       </c>
-      <c r="I38" s="168">
+      <c r="I38" s="167">
         <f t="shared" ref="I38:I43" si="9">H38</f>
         <v>265569.33</v>
       </c>
@@ -5936,20 +5927,20 @@
     </row>
     <row r="39" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B39" s="68">
         <v>12</v>
       </c>
       <c r="C39" s="68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D39" s="68">
         <f t="shared" ref="D39:D75" si="16">D38+1</f>
         <v>34</v>
       </c>
       <c r="E39" s="68" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="F39" s="68"/>
       <c r="G39" s="77">
@@ -5958,7 +5949,7 @@
       <c r="H39" s="78">
         <v>298744.34000000003</v>
       </c>
-      <c r="I39" s="168">
+      <c r="I39" s="167">
         <f t="shared" si="9"/>
         <v>298744.34000000003</v>
       </c>
@@ -6000,23 +5991,23 @@
     </row>
     <row r="40" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B40" s="68">
         <v>1</v>
       </c>
       <c r="C40" s="68" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D40" s="68">
         <f t="shared" si="16"/>
         <v>35</v>
       </c>
       <c r="E40" s="68" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="F40" s="69" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="G40" s="77">
         <v>1.0069999999999999</v>
@@ -6024,7 +6015,7 @@
       <c r="H40" s="78">
         <v>118205.35</v>
       </c>
-      <c r="I40" s="168">
+      <c r="I40" s="167">
         <f t="shared" si="9"/>
         <v>118205.35</v>
       </c>
@@ -6066,23 +6057,23 @@
     </row>
     <row r="41" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B41" s="68">
         <v>1</v>
       </c>
       <c r="C41" s="68" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D41" s="68">
         <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="E41" s="68" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="F41" s="69" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="G41" s="77">
         <v>0.78120000000000001</v>
@@ -6090,7 +6081,7 @@
       <c r="H41" s="79">
         <v>88876.36</v>
       </c>
-      <c r="I41" s="168">
+      <c r="I41" s="167">
         <f t="shared" si="9"/>
         <v>88876.36</v>
       </c>
@@ -6130,7 +6121,7 @@
         <v>0.36000000000000015</v>
       </c>
       <c r="U41" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6139,17 +6130,17 @@
         <v>1</v>
       </c>
       <c r="C42" s="67" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D42" s="68">
         <f t="shared" si="16"/>
         <v>37</v>
       </c>
       <c r="E42" s="67" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="F42" s="69" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="G42" s="91">
         <v>1.2153</v>
@@ -6157,7 +6148,7 @@
       <c r="H42" s="78">
         <v>138263.37</v>
       </c>
-      <c r="I42" s="168">
+      <c r="I42" s="167">
         <f t="shared" si="9"/>
         <v>138263.37</v>
       </c>
@@ -6197,7 +6188,7 @@
         <v>0.37000000000000016</v>
       </c>
       <c r="U42" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6205,17 +6196,17 @@
         <v>2</v>
       </c>
       <c r="C43" s="92" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D43" s="68">
         <f t="shared" si="16"/>
         <v>38</v>
       </c>
       <c r="E43" s="67" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F43" s="67" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="G43" s="91">
         <v>0.95489999999999997</v>
@@ -6223,7 +6214,7 @@
       <c r="H43" s="78">
         <v>111896</v>
       </c>
-      <c r="I43" s="168">
+      <c r="I43" s="167">
         <f t="shared" si="9"/>
         <v>111896</v>
       </c>
@@ -6268,14 +6259,14 @@
         <v>2</v>
       </c>
       <c r="C44" s="92" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D44" s="68">
         <f t="shared" si="16"/>
         <v>39</v>
       </c>
       <c r="E44" s="67" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F44" s="90"/>
       <c r="G44" s="91">
@@ -6284,7 +6275,7 @@
       <c r="H44" s="78">
         <v>429687.39</v>
       </c>
-      <c r="I44" s="168"/>
+      <c r="I44" s="167"/>
       <c r="J44" s="80"/>
       <c r="K44" s="81">
         <f t="shared" si="10"/>
@@ -6326,17 +6317,17 @@
         <v>2</v>
       </c>
       <c r="C45" s="92" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D45" s="68">
         <f t="shared" si="16"/>
         <v>40</v>
       </c>
       <c r="E45" s="67" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F45" s="67" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="G45" s="91">
         <v>1.1545000000000001</v>
@@ -6344,7 +6335,7 @@
       <c r="H45" s="78">
         <v>131346.4</v>
       </c>
-      <c r="I45" s="168">
+      <c r="I45" s="167">
         <v>135296.4</v>
       </c>
       <c r="J45" s="80"/>
@@ -6388,17 +6379,17 @@
         <v>3</v>
       </c>
       <c r="C46" s="92" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D46" s="68">
         <f t="shared" si="16"/>
         <v>41</v>
       </c>
       <c r="E46" s="67" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="F46" s="67" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="G46" s="91">
         <v>0.95489999999999997</v>
@@ -6406,7 +6397,7 @@
       <c r="H46" s="78">
         <v>108637.41</v>
       </c>
-      <c r="I46" s="168">
+      <c r="I46" s="167">
         <v>111896.41</v>
       </c>
       <c r="J46" s="80"/>
@@ -6450,14 +6441,14 @@
         <v>3</v>
       </c>
       <c r="C47" s="92" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D47" s="68">
         <f t="shared" si="16"/>
         <v>42</v>
       </c>
       <c r="E47" s="67" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="F47" s="90"/>
       <c r="G47" s="91">
@@ -6466,7 +6457,7 @@
       <c r="H47" s="78">
         <v>85918.42</v>
       </c>
-      <c r="I47" s="168">
+      <c r="I47" s="167">
         <f>H47</f>
         <v>85918.42</v>
       </c>
@@ -6511,14 +6502,14 @@
         <v>3</v>
       </c>
       <c r="C48" s="92" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D48" s="68">
         <f t="shared" si="16"/>
         <v>43</v>
       </c>
       <c r="E48" s="67" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="F48" s="90"/>
       <c r="G48" s="91">
@@ -6527,7 +6518,7 @@
       <c r="H48" s="78">
         <v>131346.43</v>
       </c>
-      <c r="I48" s="168">
+      <c r="I48" s="167">
         <f>H48</f>
         <v>131346.43</v>
       </c>
@@ -6572,17 +6563,17 @@
         <v>4</v>
       </c>
       <c r="C49" s="92" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D49" s="68">
         <f t="shared" si="16"/>
         <v>44</v>
       </c>
       <c r="E49" s="67" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="F49" s="90" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="G49" s="91">
         <v>0.95489999999999997</v>
@@ -6590,7 +6581,7 @@
       <c r="H49" s="78">
         <v>108637.44</v>
       </c>
-      <c r="I49" s="168">
+      <c r="I49" s="167">
         <f>H49</f>
         <v>108637.44</v>
       </c>
@@ -6635,14 +6626,14 @@
         <v>4</v>
       </c>
       <c r="C50" s="92" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D50" s="68">
         <f t="shared" si="16"/>
         <v>45</v>
       </c>
       <c r="E50" s="67" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F50" s="67"/>
       <c r="G50" s="91">
@@ -6651,7 +6642,7 @@
       <c r="H50" s="78">
         <v>85918.45</v>
       </c>
-      <c r="I50" s="168">
+      <c r="I50" s="167">
         <v>85920</v>
       </c>
       <c r="J50" s="80"/>
@@ -6690,7 +6681,7 @@
         <v>0.45000000000000023</v>
       </c>
       <c r="U50" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
     </row>
     <row r="51" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6698,17 +6689,17 @@
         <v>4</v>
       </c>
       <c r="C51" s="92" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D51" s="68">
         <f t="shared" si="16"/>
         <v>46</v>
       </c>
       <c r="E51" s="67" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="F51" s="67" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G51" s="91">
         <v>1.1545000000000001</v>
@@ -6716,7 +6707,7 @@
       <c r="H51" s="78">
         <v>131346.46</v>
       </c>
-      <c r="I51" s="168">
+      <c r="I51" s="167">
         <f t="shared" ref="I51:I59" si="18">H51</f>
         <v>131346.46</v>
       </c>
@@ -6761,17 +6752,17 @@
         <v>5</v>
       </c>
       <c r="C52" s="92" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D52" s="68">
         <f t="shared" si="16"/>
         <v>47</v>
       </c>
       <c r="E52" s="67" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="F52" s="90" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="G52" s="91">
         <v>0.95489999999999997</v>
@@ -6779,7 +6770,7 @@
       <c r="H52" s="78">
         <v>108637.47</v>
       </c>
-      <c r="I52" s="168">
+      <c r="I52" s="167">
         <f t="shared" si="18"/>
         <v>108637.47</v>
       </c>
@@ -6824,17 +6815,17 @@
         <v>5</v>
       </c>
       <c r="C53" s="92" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D53" s="68">
         <f t="shared" si="16"/>
         <v>48</v>
       </c>
       <c r="E53" s="67" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F53" s="67" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="G53" s="91">
         <v>0.75519999999999998</v>
@@ -6842,7 +6833,7 @@
       <c r="H53" s="78">
         <v>85918.48</v>
       </c>
-      <c r="I53" s="168">
+      <c r="I53" s="167">
         <f t="shared" si="18"/>
         <v>85918.48</v>
       </c>
@@ -6887,17 +6878,17 @@
         <v>5</v>
       </c>
       <c r="C54" s="92" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D54" s="68">
         <f t="shared" si="16"/>
         <v>49</v>
       </c>
       <c r="E54" s="67" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="F54" s="67" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="G54" s="91">
         <v>1.1545000000000001</v>
@@ -6905,7 +6896,7 @@
       <c r="H54" s="78">
         <v>135404.49</v>
       </c>
-      <c r="I54" s="168">
+      <c r="I54" s="167">
         <f t="shared" si="18"/>
         <v>135404.49</v>
       </c>
@@ -6950,14 +6941,14 @@
         <v>6</v>
       </c>
       <c r="C55" s="92" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D55" s="68">
         <f t="shared" si="16"/>
         <v>50</v>
       </c>
       <c r="E55" s="67" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F55" s="67"/>
       <c r="G55" s="91">
@@ -6966,7 +6957,7 @@
       <c r="H55" s="78">
         <v>108637.5</v>
       </c>
-      <c r="I55" s="168">
+      <c r="I55" s="167">
         <f t="shared" si="18"/>
         <v>108637.5</v>
       </c>
@@ -7011,14 +7002,14 @@
         <v>6</v>
       </c>
       <c r="C56" s="92" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D56" s="68">
         <f t="shared" si="16"/>
         <v>51</v>
       </c>
       <c r="E56" s="67" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="F56" s="67"/>
       <c r="G56" s="91">
@@ -7027,7 +7018,7 @@
       <c r="H56" s="78">
         <v>88469.51</v>
       </c>
-      <c r="I56" s="168">
+      <c r="I56" s="167">
         <f t="shared" si="18"/>
         <v>88469.51</v>
       </c>
@@ -7067,7 +7058,7 @@
         <v>0.51000000000000023</v>
       </c>
       <c r="U56" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="57" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7075,14 +7066,14 @@
         <v>6</v>
       </c>
       <c r="C57" s="92" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D57" s="68">
         <f t="shared" si="16"/>
         <v>52</v>
       </c>
       <c r="E57" s="67" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F57" s="90"/>
       <c r="G57" s="91">
@@ -7091,7 +7082,7 @@
       <c r="H57" s="78">
         <v>270502.52</v>
       </c>
-      <c r="I57" s="168">
+      <c r="I57" s="167">
         <f t="shared" si="18"/>
         <v>270502.52</v>
       </c>
@@ -7136,14 +7127,14 @@
         <v>7</v>
       </c>
       <c r="C58" s="92" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D58" s="68">
         <f t="shared" si="16"/>
         <v>53</v>
       </c>
       <c r="E58" s="67" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="F58" s="90"/>
       <c r="G58" s="91">
@@ -7152,7 +7143,7 @@
       <c r="H58" s="78">
         <v>108637.53</v>
       </c>
-      <c r="I58" s="168">
+      <c r="I58" s="167">
         <f t="shared" si="18"/>
         <v>108637.53</v>
       </c>
@@ -7197,14 +7188,14 @@
         <v>7</v>
       </c>
       <c r="C59" s="92" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D59" s="68">
         <f t="shared" si="16"/>
         <v>54</v>
       </c>
       <c r="E59" s="67" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="F59" s="67"/>
       <c r="G59" s="91">
@@ -7213,7 +7204,7 @@
       <c r="H59" s="78">
         <v>85918.54</v>
       </c>
-      <c r="I59" s="168">
+      <c r="I59" s="167">
         <f t="shared" si="18"/>
         <v>85918.54</v>
       </c>
@@ -7258,17 +7249,17 @@
         <v>7</v>
       </c>
       <c r="C60" s="92" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D60" s="68">
         <f t="shared" si="16"/>
         <v>55</v>
       </c>
       <c r="E60" s="67" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="F60" s="67" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="G60" s="91">
         <v>1.1545000000000001</v>
@@ -7276,7 +7267,7 @@
       <c r="H60" s="78">
         <v>534759.55000000005</v>
       </c>
-      <c r="I60" s="168">
+      <c r="I60" s="167">
         <v>119858</v>
       </c>
       <c r="J60" s="80"/>
@@ -7320,17 +7311,17 @@
         <v>8</v>
       </c>
       <c r="C61" s="92" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D61" s="68">
         <f t="shared" si="16"/>
         <v>56</v>
       </c>
       <c r="E61" s="67" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="F61" s="90" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="G61" s="91">
         <v>0.95489999999999997</v>
@@ -7338,7 +7329,7 @@
       <c r="H61" s="78">
         <v>108637.56</v>
       </c>
-      <c r="I61" s="168">
+      <c r="I61" s="167">
         <f>H61</f>
         <v>108637.56</v>
       </c>
@@ -7381,17 +7372,17 @@
         <v>8</v>
       </c>
       <c r="C62" s="92" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D62" s="68">
         <f t="shared" si="16"/>
         <v>57</v>
       </c>
       <c r="E62" s="67" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="F62" s="90" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="G62" s="91">
         <v>0.75519999999999998</v>
@@ -7399,7 +7390,7 @@
       <c r="H62" s="78">
         <v>85918.57</v>
       </c>
-      <c r="I62" s="168">
+      <c r="I62" s="167">
         <v>85496.57</v>
       </c>
       <c r="J62" s="80"/>
@@ -7443,14 +7434,14 @@
         <v>8</v>
       </c>
       <c r="C63" s="92" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D63" s="68">
         <f t="shared" si="16"/>
         <v>58</v>
       </c>
       <c r="E63" s="67" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="F63" s="90"/>
       <c r="G63" s="91">
@@ -7459,7 +7450,7 @@
       <c r="H63" s="78">
         <v>131346.57999999999</v>
       </c>
-      <c r="I63" s="168">
+      <c r="I63" s="167">
         <f>H63</f>
         <v>131346.57999999999</v>
       </c>
@@ -7504,17 +7495,17 @@
         <v>9</v>
       </c>
       <c r="C64" s="92" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D64" s="68">
         <f t="shared" si="16"/>
         <v>59</v>
       </c>
       <c r="E64" s="67" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="F64" s="67" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="G64" s="91">
         <v>0.95489999999999997</v>
@@ -7522,7 +7513,7 @@
       <c r="H64" s="78">
         <v>220534.59</v>
       </c>
-      <c r="I64" s="168">
+      <c r="I64" s="167">
         <v>108637</v>
       </c>
       <c r="J64" s="80"/>
@@ -7566,14 +7557,14 @@
         <v>9</v>
       </c>
       <c r="C65" s="92" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D65" s="68">
         <f t="shared" si="16"/>
         <v>60</v>
       </c>
       <c r="E65" s="67" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="F65" s="90"/>
       <c r="G65" s="91">
@@ -7582,7 +7573,7 @@
       <c r="H65" s="78">
         <v>88496</v>
       </c>
-      <c r="I65" s="168">
+      <c r="I65" s="167">
         <v>85918</v>
       </c>
       <c r="J65" s="80"/>
@@ -7621,7 +7612,7 @@
         <v>0.60000000000000031</v>
       </c>
       <c r="U65" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="66" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7629,14 +7620,14 @@
         <v>9</v>
       </c>
       <c r="C66" s="92" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D66" s="68">
         <f t="shared" si="16"/>
         <v>61</v>
       </c>
       <c r="E66" s="67" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="F66" s="67"/>
       <c r="G66" s="91">
@@ -7645,7 +7636,7 @@
       <c r="H66" s="78">
         <v>131346.60999999999</v>
       </c>
-      <c r="I66" s="168">
+      <c r="I66" s="167">
         <f>H66</f>
         <v>131346.60999999999</v>
       </c>
@@ -7685,7 +7676,7 @@
         <v>0.61000000000000032</v>
       </c>
       <c r="U66" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="67" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7693,17 +7684,17 @@
         <v>10</v>
       </c>
       <c r="C67" s="92" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D67" s="68">
         <f t="shared" si="16"/>
         <v>62</v>
       </c>
       <c r="E67" s="67" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="F67" s="90" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="G67" s="91">
         <v>0.95489999999999997</v>
@@ -7711,7 +7702,7 @@
       <c r="H67" s="78">
         <v>108638.62</v>
       </c>
-      <c r="I67" s="168">
+      <c r="I67" s="167">
         <f>H67</f>
         <v>108638.62</v>
       </c>
@@ -7751,7 +7742,7 @@
         <v>0.62000000000000033</v>
       </c>
       <c r="U67" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="68" spans="2:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7759,17 +7750,17 @@
         <v>10</v>
       </c>
       <c r="C68" s="92" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D68" s="68">
         <f t="shared" si="16"/>
         <v>63</v>
       </c>
       <c r="E68" s="67" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F68" s="67" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="G68" s="91">
         <v>0.75519999999999998</v>
@@ -7777,7 +7768,7 @@
       <c r="H68" s="78">
         <v>88412.63</v>
       </c>
-      <c r="I68" s="168">
+      <c r="I68" s="167">
         <v>85918.63</v>
       </c>
       <c r="J68" s="80"/>
@@ -7821,14 +7812,14 @@
         <v>10</v>
       </c>
       <c r="C69" s="92" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D69" s="68">
         <f t="shared" si="16"/>
         <v>64</v>
       </c>
       <c r="E69" s="67" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="F69" s="67"/>
       <c r="G69" s="91">
@@ -7837,7 +7828,7 @@
       <c r="H69" s="78">
         <v>131346.64000000001</v>
       </c>
-      <c r="I69" s="168">
+      <c r="I69" s="167">
         <f>H69</f>
         <v>131346.64000000001</v>
       </c>
@@ -7882,14 +7873,14 @@
         <v>11</v>
       </c>
       <c r="C70" s="92" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D70" s="68">
         <f t="shared" si="16"/>
         <v>65</v>
       </c>
       <c r="E70" s="67" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="F70" s="90"/>
       <c r="G70" s="91">
@@ -7898,7 +7889,7 @@
       <c r="H70" s="78">
         <v>108637.65</v>
       </c>
-      <c r="I70" s="168">
+      <c r="I70" s="167">
         <f>H70</f>
         <v>108637.65</v>
       </c>
@@ -7908,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="81">
-        <f t="shared" ref="L70:L101" si="20">IF(K70&gt;0,K70*3%,0)</f>
+        <f t="shared" ref="L70:L75" si="20">IF(K70&gt;0,K70*3%,0)</f>
         <v>0</v>
       </c>
       <c r="M70" s="82">
@@ -7922,11 +7913,11 @@
         <v>0</v>
       </c>
       <c r="P70" s="85">
-        <f t="shared" ref="P70:P101" si="22">ROUND(SUM(K70:O70),0) + S70</f>
+        <f t="shared" ref="P70:P75" si="22">ROUND(SUM(K70:O70),0) + S70</f>
         <v>118186.65</v>
       </c>
       <c r="Q70" s="86">
-        <f t="shared" ref="Q70:Q101" si="23">ROUND(P70*6% + P70,0) + S70</f>
+        <f t="shared" ref="Q70:Q75" si="23">ROUND(P70*6% + P70,0) + S70</f>
         <v>125278.65</v>
       </c>
       <c r="R70" s="87">
@@ -7943,17 +7934,17 @@
         <v>11</v>
       </c>
       <c r="C71" s="92" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D71" s="68">
         <f t="shared" si="16"/>
         <v>66</v>
       </c>
       <c r="E71" s="67" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F71" s="90" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="G71" s="91">
         <v>0.75519999999999998</v>
@@ -7961,7 +7952,7 @@
       <c r="H71" s="78">
         <v>85918.66</v>
       </c>
-      <c r="I71" s="168">
+      <c r="I71" s="167">
         <v>88496.66</v>
       </c>
       <c r="J71" s="80"/>
@@ -8005,14 +7996,14 @@
         <v>11</v>
       </c>
       <c r="C72" s="92" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D72" s="68">
         <f t="shared" si="16"/>
         <v>67</v>
       </c>
       <c r="E72" s="67" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="F72" s="67"/>
       <c r="G72" s="91">
@@ -8021,7 +8012,7 @@
       <c r="H72" s="78">
         <v>131346.67000000001</v>
       </c>
-      <c r="I72" s="168">
+      <c r="I72" s="167">
         <f>H72</f>
         <v>131346.67000000001</v>
       </c>
@@ -8066,14 +8057,14 @@
         <v>12</v>
       </c>
       <c r="C73" s="93" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D73" s="68">
         <f t="shared" si="16"/>
         <v>68</v>
       </c>
       <c r="E73" s="94" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="F73" s="94"/>
       <c r="G73" s="95">
@@ -8082,7 +8073,7 @@
       <c r="H73" s="96">
         <v>108637.68</v>
       </c>
-      <c r="I73" s="168">
+      <c r="I73" s="167">
         <f>H73</f>
         <v>108637.68</v>
       </c>
@@ -8127,14 +8118,14 @@
         <v>12</v>
       </c>
       <c r="C74" s="92" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D74" s="68">
         <f t="shared" si="16"/>
         <v>69</v>
       </c>
       <c r="E74" s="68" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="F74" s="102"/>
       <c r="G74" s="95">
@@ -8143,7 +8134,7 @@
       <c r="H74" s="96">
         <v>85918.69</v>
       </c>
-      <c r="I74" s="168">
+      <c r="I74" s="167">
         <f>H74</f>
         <v>85918.69</v>
       </c>
@@ -8188,14 +8179,14 @@
         <v>12</v>
       </c>
       <c r="C75" s="92" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D75" s="68">
         <f t="shared" si="16"/>
         <v>70</v>
       </c>
       <c r="E75" s="68" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="F75" s="102"/>
       <c r="G75" s="95">
@@ -8204,7 +8195,7 @@
       <c r="H75" s="96">
         <v>131391.70000000001</v>
       </c>
-      <c r="I75" s="168">
+      <c r="I75" s="167">
         <f>H75</f>
         <v>131391.70000000001</v>
       </c>
@@ -8399,94 +8390,102 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="220" t="str">
+      <c r="E84" s="213" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="214"/>
-      <c r="G84" s="214"/>
-      <c r="H84" s="214"/>
-      <c r="I84" s="214"/>
-      <c r="J84" s="214"/>
-      <c r="K84" s="214"/>
-      <c r="L84" s="214"/>
-      <c r="M84" s="214"/>
-      <c r="N84" s="214"/>
-      <c r="O84" s="214"/>
-      <c r="P84" s="214"/>
+      <c r="F84" s="208"/>
+      <c r="G84" s="208"/>
+      <c r="H84" s="208"/>
+      <c r="I84" s="208"/>
+      <c r="J84" s="208"/>
+      <c r="K84" s="208"/>
+      <c r="L84" s="208"/>
+      <c r="M84" s="208"/>
+      <c r="N84" s="208"/>
+      <c r="O84" s="208"/>
+      <c r="P84" s="208"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="214"/>
-      <c r="F85" s="214"/>
-      <c r="G85" s="214"/>
-      <c r="H85" s="214"/>
-      <c r="I85" s="214"/>
-      <c r="J85" s="214"/>
-      <c r="K85" s="214"/>
-      <c r="L85" s="214"/>
-      <c r="M85" s="214"/>
-      <c r="N85" s="214"/>
-      <c r="O85" s="214"/>
-      <c r="P85" s="214"/>
+      <c r="E85" s="208"/>
+      <c r="F85" s="208"/>
+      <c r="G85" s="208"/>
+      <c r="H85" s="208"/>
+      <c r="I85" s="208"/>
+      <c r="J85" s="208"/>
+      <c r="K85" s="208"/>
+      <c r="L85" s="208"/>
+      <c r="M85" s="208"/>
+      <c r="N85" s="208"/>
+      <c r="O85" s="208"/>
+      <c r="P85" s="208"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="214"/>
-      <c r="F86" s="214"/>
-      <c r="G86" s="214"/>
-      <c r="H86" s="214"/>
-      <c r="I86" s="214"/>
-      <c r="J86" s="214"/>
-      <c r="K86" s="214"/>
-      <c r="L86" s="214"/>
-      <c r="M86" s="214"/>
-      <c r="N86" s="214"/>
-      <c r="O86" s="214"/>
-      <c r="P86" s="214"/>
+      <c r="E86" s="208"/>
+      <c r="F86" s="208"/>
+      <c r="G86" s="208"/>
+      <c r="H86" s="208"/>
+      <c r="I86" s="208"/>
+      <c r="J86" s="208"/>
+      <c r="K86" s="208"/>
+      <c r="L86" s="208"/>
+      <c r="M86" s="208"/>
+      <c r="N86" s="208"/>
+      <c r="O86" s="208"/>
+      <c r="P86" s="208"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="214"/>
-      <c r="F87" s="214"/>
-      <c r="G87" s="214"/>
-      <c r="H87" s="214"/>
-      <c r="I87" s="214"/>
-      <c r="J87" s="214"/>
-      <c r="K87" s="214"/>
-      <c r="L87" s="214"/>
-      <c r="M87" s="214"/>
-      <c r="N87" s="214"/>
-      <c r="O87" s="214"/>
-      <c r="P87" s="214"/>
+      <c r="E87" s="208"/>
+      <c r="F87" s="208"/>
+      <c r="G87" s="208"/>
+      <c r="H87" s="208"/>
+      <c r="I87" s="208"/>
+      <c r="J87" s="208"/>
+      <c r="K87" s="208"/>
+      <c r="L87" s="208"/>
+      <c r="M87" s="208"/>
+      <c r="N87" s="208"/>
+      <c r="O87" s="208"/>
+      <c r="P87" s="208"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="214"/>
-      <c r="F88" s="214"/>
-      <c r="G88" s="214"/>
-      <c r="H88" s="214"/>
-      <c r="I88" s="214"/>
-      <c r="J88" s="214"/>
-      <c r="K88" s="214"/>
-      <c r="L88" s="214"/>
-      <c r="M88" s="214"/>
-      <c r="N88" s="214"/>
-      <c r="O88" s="214"/>
-      <c r="P88" s="214"/>
+      <c r="E88" s="208"/>
+      <c r="F88" s="208"/>
+      <c r="G88" s="208"/>
+      <c r="H88" s="208"/>
+      <c r="I88" s="208"/>
+      <c r="J88" s="208"/>
+      <c r="K88" s="208"/>
+      <c r="L88" s="208"/>
+      <c r="M88" s="208"/>
+      <c r="N88" s="208"/>
+      <c r="O88" s="208"/>
+      <c r="P88" s="208"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="214"/>
-      <c r="F89" s="214"/>
-      <c r="G89" s="214"/>
-      <c r="H89" s="214"/>
-      <c r="I89" s="214"/>
-      <c r="J89" s="214"/>
-      <c r="K89" s="214"/>
-      <c r="L89" s="214"/>
-      <c r="M89" s="214"/>
-      <c r="N89" s="214"/>
-      <c r="O89" s="214"/>
-      <c r="P89" s="214"/>
+      <c r="E89" s="208"/>
+      <c r="F89" s="208"/>
+      <c r="G89" s="208"/>
+      <c r="H89" s="208"/>
+      <c r="I89" s="208"/>
+      <c r="J89" s="208"/>
+      <c r="K89" s="208"/>
+      <c r="L89" s="208"/>
+      <c r="M89" s="208"/>
+      <c r="N89" s="208"/>
+      <c r="O89" s="208"/>
+      <c r="P89" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="G1:P1"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
     <mergeCell ref="E84:P89"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="J4:J5"/>
@@ -8498,14 +8497,6 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="H4:H5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="G1:P1"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -8518,8 +8509,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="5" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C5" s="209" t="s">
-        <v>248</v>
+      <c r="C5" s="206" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/GORRITI/Junio/GORRITI-JUNIO.xlsx
+++ b/GORRITI/Junio/GORRITI-JUNIO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\GORRITI\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7180E2-EEBB-459A-8A68-BB755341E647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CF83AB-B0C8-435D-94A4-E5DC1DF81C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -646,9 +646,6 @@
     <t>DE BIAGGIO PABLO</t>
   </si>
   <si>
-    <t>LUCIANA TIENE TODO PAGO, CORREGIR ESO</t>
-  </si>
-  <si>
     <t>PERÍODO: JUNIO</t>
   </si>
   <si>
@@ -752,6 +749,9 @@
   </si>
   <si>
     <t>PREVISION ORDINARIA - ARREGLO DE ASCENSOR</t>
+  </si>
+  <si>
+    <t>PABLO DI COIRO TIENE A FAVOR 280 MIL PESOS - PINTURA OSCAR</t>
   </si>
 </sst>
 </file>
@@ -1501,7 +1501,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1802,16 +1802,26 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="171" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1823,22 +1833,32 @@
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1850,29 +1870,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2304,7 +2305,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C6" s="207"/>
       <c r="D6" s="200" t="s">
@@ -2324,49 +2325,49 @@
       <c r="E7" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="212" t="s">
+      <c r="B9" s="218" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="213"/>
+      <c r="C9" s="212"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="213"/>
-      <c r="C10" s="213"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="212"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="213"/>
-      <c r="C11" s="213"/>
+      <c r="B11" s="212"/>
+      <c r="C11" s="212"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="218" t="s">
+      <c r="A14" s="222" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="213"/>
-      <c r="C14" s="213"/>
-      <c r="D14" s="213"/>
-      <c r="E14" s="213"/>
+      <c r="B14" s="212"/>
+      <c r="C14" s="212"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="212"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="213"/>
-      <c r="B15" s="213"/>
-      <c r="C15" s="213"/>
-      <c r="D15" s="213"/>
-      <c r="E15" s="213"/>
+      <c r="A15" s="212"/>
+      <c r="B15" s="212"/>
+      <c r="C15" s="212"/>
+      <c r="D15" s="212"/>
+      <c r="E15" s="212"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="213"/>
-      <c r="B16" s="213"/>
-      <c r="C16" s="213"/>
-      <c r="D16" s="213"/>
-      <c r="E16" s="213"/>
+      <c r="A16" s="212"/>
+      <c r="B16" s="212"/>
+      <c r="C16" s="212"/>
+      <c r="D16" s="212"/>
+      <c r="E16" s="212"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="213"/>
-      <c r="B17" s="213"/>
-      <c r="C17" s="213"/>
-      <c r="D17" s="213"/>
-      <c r="E17" s="213"/>
+      <c r="A17" s="212"/>
+      <c r="B17" s="212"/>
+      <c r="C17" s="212"/>
+      <c r="D17" s="212"/>
+      <c r="E17" s="212"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2396,14 +2397,14 @@
         <v>14</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="160">
         <v>1879916</v>
       </c>
       <c r="E23" s="155" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -2460,7 +2461,7 @@
         <v>17</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="160">
@@ -2570,29 +2571,29 @@
       <c r="E39" s="168"/>
     </row>
     <row r="40" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="217" t="s">
-        <v>216</v>
-      </c>
-      <c r="B40" s="211"/>
+      <c r="A40" s="221" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" s="214"/>
       <c r="C40" s="190"/>
       <c r="D40" s="160">
         <v>56000</v>
       </c>
       <c r="E40" s="189" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="214" t="s">
-        <v>209</v>
-      </c>
-      <c r="B41" s="211"/>
+      <c r="A41" s="213" t="s">
+        <v>208</v>
+      </c>
+      <c r="B41" s="214"/>
       <c r="C41" s="52"/>
       <c r="D41" s="160">
         <v>249000</v>
       </c>
       <c r="E41" s="189" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H41" s="139"/>
     </row>
@@ -2618,21 +2619,21 @@
       <c r="E43" s="172"/>
     </row>
     <row r="44" spans="1:8" s="37" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="210" t="s">
+      <c r="A44" s="215" t="s">
         <v>25</v>
       </c>
-      <c r="B44" s="211"/>
+      <c r="B44" s="214"/>
       <c r="C44" s="54"/>
       <c r="D44" s="198">
         <v>120977</v>
       </c>
       <c r="E44" s="173" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="210"/>
-      <c r="B45" s="211"/>
+      <c r="A45" s="215"/>
+      <c r="B45" s="214"/>
       <c r="C45" s="54"/>
       <c r="D45" s="174"/>
       <c r="E45" s="173"/>
@@ -2668,13 +2669,13 @@
         <v>1688376.15</v>
       </c>
       <c r="E48" s="177" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G48" s="139"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>29</v>
@@ -2684,7 +2685,7 @@
         <v>132484</v>
       </c>
       <c r="E49" s="178" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2752,7 +2753,7 @@
         <v>907716.3</v>
       </c>
       <c r="E54" s="187" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2765,7 +2766,7 @@
         <v>11144.38</v>
       </c>
       <c r="E55" s="187" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2798,7 +2799,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2807,12 +2808,12 @@
         <v>4753.74</v>
       </c>
       <c r="E58" s="194" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2820,12 +2821,12 @@
         <v>5015.88</v>
       </c>
       <c r="E59" s="194" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -2833,12 +2834,12 @@
         <v>5348.66</v>
       </c>
       <c r="E60" s="194" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2846,7 +2847,7 @@
         <v>571919</v>
       </c>
       <c r="E61" s="181" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -2859,28 +2860,28 @@
         <v>22603.51</v>
       </c>
       <c r="E62" s="194" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="210" t="s">
+      <c r="A63" s="215" t="s">
         <v>39</v>
       </c>
-      <c r="B63" s="211"/>
+      <c r="B63" s="214"/>
       <c r="C63" s="5"/>
       <c r="D63" s="174">
         <v>2302294.3199999998</v>
       </c>
       <c r="E63" s="194" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="210"/>
-      <c r="B64" s="211"/>
+      <c r="A64" s="215"/>
+      <c r="B64" s="214"/>
       <c r="C64" s="157"/>
-      <c r="D64" s="215"/>
-      <c r="E64" s="216"/>
+      <c r="D64" s="219"/>
+      <c r="E64" s="220"/>
     </row>
     <row r="65" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="28" t="s">
@@ -2904,16 +2905,16 @@
       <c r="E66" s="183"/>
     </row>
     <row r="67" spans="1:10" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="214" t="s">
-        <v>233</v>
-      </c>
-      <c r="B67" s="211"/>
+      <c r="A67" s="213" t="s">
+        <v>232</v>
+      </c>
+      <c r="B67" s="214"/>
       <c r="C67" s="55"/>
       <c r="D67" s="174">
         <v>96800</v>
       </c>
       <c r="E67" s="187" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -2926,7 +2927,7 @@
         <v>54600</v>
       </c>
       <c r="E68" s="187" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -2939,27 +2940,27 @@
         <v>120000</v>
       </c>
       <c r="E69" s="188" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="215" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" ht="69" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="210" t="s">
-        <v>213</v>
-      </c>
-      <c r="B70" s="211"/>
+      <c r="B70" s="214"/>
       <c r="C70" s="5"/>
       <c r="D70" s="174">
         <v>190500</v>
       </c>
       <c r="E70" s="188" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="214" t="s">
-        <v>232</v>
-      </c>
-      <c r="B71" s="219"/>
+      <c r="A71" s="213" t="s">
+        <v>231</v>
+      </c>
+      <c r="B71" s="216"/>
       <c r="C71" s="5"/>
       <c r="D71" s="174">
         <v>-240000</v>
@@ -2967,53 +2968,53 @@
       <c r="E71" s="188"/>
     </row>
     <row r="72" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="214" t="s">
-        <v>230</v>
-      </c>
-      <c r="B72" s="219"/>
+      <c r="A72" s="213" t="s">
+        <v>229</v>
+      </c>
+      <c r="B72" s="216"/>
       <c r="C72" s="5"/>
       <c r="D72" s="117">
         <v>450000</v>
       </c>
       <c r="E72" s="182" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="214" t="s">
-        <v>218</v>
-      </c>
-      <c r="B73" s="211"/>
+      <c r="A73" s="213" t="s">
+        <v>217</v>
+      </c>
+      <c r="B73" s="214"/>
       <c r="C73" s="5"/>
       <c r="D73" s="117">
         <v>85000</v>
       </c>
       <c r="E73" s="182" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="214" t="s">
-        <v>220</v>
-      </c>
-      <c r="B74" s="219"/>
+      <c r="A74" s="213" t="s">
+        <v>219</v>
+      </c>
+      <c r="B74" s="216"/>
       <c r="C74" s="5"/>
       <c r="D74" s="117">
         <f>178500</f>
         <v>178500</v>
       </c>
       <c r="E74" s="182" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="210"/>
-      <c r="B75" s="211"/>
+      <c r="A75" s="215"/>
+      <c r="B75" s="214"/>
       <c r="C75" s="5"/>
       <c r="D75" s="117"/>
       <c r="E75" s="184"/>
-      <c r="I75" s="210"/>
-      <c r="J75" s="211"/>
+      <c r="I75" s="215"/>
+      <c r="J75" s="214"/>
     </row>
     <row r="76" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="28" t="s">
@@ -3050,14 +3051,14 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="174"/>
       <c r="E79" s="119"/>
       <c r="G79" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3081,7 +3082,7 @@
     </row>
     <row r="82" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="29" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B82" s="29"/>
       <c r="C82" s="29"/>
@@ -3132,22 +3133,22 @@
       <c r="E87" s="129"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="210"/>
-      <c r="B88" s="211"/>
+      <c r="A88" s="215"/>
+      <c r="B88" s="214"/>
       <c r="C88" s="5"/>
       <c r="D88" s="144"/>
       <c r="E88" s="115"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="210"/>
-      <c r="B89" s="211"/>
+      <c r="A89" s="215"/>
+      <c r="B89" s="214"/>
       <c r="C89" s="5"/>
       <c r="D89" s="117"/>
       <c r="E89" s="115"/>
     </row>
     <row r="90" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="214"/>
-      <c r="B90" s="211"/>
+      <c r="A90" s="213"/>
+      <c r="B90" s="214"/>
       <c r="C90" s="5"/>
       <c r="D90" s="117"/>
       <c r="E90" s="115"/>
@@ -3232,25 +3233,25 @@
     </row>
     <row r="103" spans="1:5" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="220"/>
-      <c r="B104" s="213"/>
-      <c r="C104" s="213"/>
-      <c r="D104" s="213"/>
-      <c r="E104" s="213"/>
+      <c r="A104" s="211"/>
+      <c r="B104" s="212"/>
+      <c r="C104" s="212"/>
+      <c r="D104" s="212"/>
+      <c r="E104" s="212"/>
     </row>
     <row r="105" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="213"/>
-      <c r="B105" s="213"/>
-      <c r="C105" s="213"/>
-      <c r="D105" s="213"/>
-      <c r="E105" s="213"/>
+      <c r="A105" s="212"/>
+      <c r="B105" s="212"/>
+      <c r="C105" s="212"/>
+      <c r="D105" s="212"/>
+      <c r="E105" s="212"/>
     </row>
     <row r="106" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="213"/>
-      <c r="B106" s="213"/>
-      <c r="C106" s="213"/>
-      <c r="D106" s="213"/>
-      <c r="E106" s="213"/>
+      <c r="A106" s="212"/>
+      <c r="B106" s="212"/>
+      <c r="C106" s="212"/>
+      <c r="D106" s="212"/>
+      <c r="E106" s="212"/>
     </row>
     <row r="108" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="21" t="s">
@@ -3390,15 +3391,15 @@
     </row>
     <row r="125" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="54" t="s">
-        <v>240</v>
-      </c>
-      <c r="B125" s="238">
+        <v>239</v>
+      </c>
+      <c r="B125" s="210">
         <v>-300521.3</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="54" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B126" s="208">
         <v>-184089</v>
@@ -3415,7 +3416,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="54" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B128" s="196">
         <v>-18500</v>
@@ -3445,16 +3446,16 @@
     </row>
     <row r="132" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A133" s="221" t="s">
+      <c r="A133" s="217" t="s">
         <v>67</v>
       </c>
-      <c r="B133" s="213"/>
-      <c r="C133" s="213"/>
+      <c r="B133" s="212"/>
+      <c r="C133" s="212"/>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A134" s="213"/>
-      <c r="B134" s="213"/>
-      <c r="C134" s="213"/>
+      <c r="A134" s="212"/>
+      <c r="B134" s="212"/>
+      <c r="C134" s="212"/>
     </row>
     <row r="135" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="131"/>
@@ -3482,44 +3483,35 @@
       <c r="M138" s="8"/>
     </row>
     <row r="139" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="220"/>
-      <c r="B139" s="213"/>
-      <c r="C139" s="213"/>
-      <c r="D139" s="213"/>
-      <c r="E139" s="213"/>
+      <c r="A139" s="211"/>
+      <c r="B139" s="212"/>
+      <c r="C139" s="212"/>
+      <c r="D139" s="212"/>
+      <c r="E139" s="212"/>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A140" s="213"/>
-      <c r="B140" s="213"/>
-      <c r="C140" s="213"/>
-      <c r="D140" s="213"/>
-      <c r="E140" s="213"/>
+      <c r="A140" s="212"/>
+      <c r="B140" s="212"/>
+      <c r="C140" s="212"/>
+      <c r="D140" s="212"/>
+      <c r="E140" s="212"/>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A141" s="213"/>
-      <c r="B141" s="213"/>
-      <c r="C141" s="213"/>
-      <c r="D141" s="213"/>
-      <c r="E141" s="213"/>
+      <c r="A141" s="212"/>
+      <c r="B141" s="212"/>
+      <c r="C141" s="212"/>
+      <c r="D141" s="212"/>
+      <c r="E141" s="212"/>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A142" s="213"/>
-      <c r="B142" s="213"/>
-      <c r="C142" s="213"/>
-      <c r="D142" s="213"/>
-      <c r="E142" s="213"/>
+      <c r="A142" s="212"/>
+      <c r="B142" s="212"/>
+      <c r="C142" s="212"/>
+      <c r="D142" s="212"/>
+      <c r="E142" s="212"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A139:E142"/>
-    <mergeCell ref="A104:E106"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A133:C134"/>
     <mergeCell ref="I75:J75"/>
     <mergeCell ref="B9:C11"/>
     <mergeCell ref="A73:B73"/>
@@ -3534,6 +3526,15 @@
     <mergeCell ref="A70:B70"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A139:E142"/>
+    <mergeCell ref="A104:E106"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A133:C134"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3576,16 +3577,16 @@
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
-      <c r="G1" s="228"/>
-      <c r="H1" s="213"/>
-      <c r="I1" s="213"/>
-      <c r="J1" s="213"/>
-      <c r="K1" s="213"/>
-      <c r="L1" s="213"/>
-      <c r="M1" s="213"/>
-      <c r="N1" s="213"/>
-      <c r="O1" s="213"/>
-      <c r="P1" s="213"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="212"/>
+      <c r="P1" s="212"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
@@ -3610,11 +3611,11 @@
       <c r="M2" s="7"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
-      <c r="P2" s="224">
+      <c r="P2" s="233">
         <v>12376831.439999999</v>
       </c>
-      <c r="Q2" s="213"/>
-      <c r="R2" s="213"/>
+      <c r="Q2" s="212"/>
+      <c r="R2" s="212"/>
       <c r="S2" s="20"/>
     </row>
     <row r="3" spans="1:21" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3638,82 +3639,82 @@
       <c r="R3" s="60"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="235" t="s">
+      <c r="A4" s="228" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="230" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="135"/>
-      <c r="D4" s="225" t="s">
+      <c r="D4" s="223" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="225" t="s">
+      <c r="E4" s="223" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="234" t="s">
+      <c r="F4" s="225" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="225" t="s">
+      <c r="G4" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="232" t="s">
+      <c r="H4" s="227" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="225" t="s">
+      <c r="I4" s="223" t="s">
         <v>55</v>
       </c>
-      <c r="J4" s="234" t="s">
+      <c r="J4" s="225" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="236" t="s">
+      <c r="K4" s="229" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="232" t="s">
+      <c r="L4" s="227" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="231" t="s">
+      <c r="M4" s="238" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="232" t="s">
+      <c r="N4" s="227" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="226" t="s">
+      <c r="O4" s="234" t="s">
         <v>81</v>
       </c>
       <c r="P4" s="63" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" s="229" t="s">
+      <c r="Q4" s="237" t="s">
         <v>83</v>
       </c>
-      <c r="R4" s="222" t="s">
+      <c r="R4" s="232" t="s">
         <v>84</v>
       </c>
       <c r="U4" s="43"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="223"/>
-      <c r="B5" s="230"/>
+      <c r="A5" s="224"/>
+      <c r="B5" s="231"/>
       <c r="C5" s="136"/>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
-      <c r="M5" s="223"/>
-      <c r="N5" s="233"/>
-      <c r="O5" s="227"/>
+      <c r="D5" s="224"/>
+      <c r="E5" s="224"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="226"/>
+      <c r="I5" s="224"/>
+      <c r="J5" s="226"/>
+      <c r="K5" s="226"/>
+      <c r="L5" s="226"/>
+      <c r="M5" s="224"/>
+      <c r="N5" s="226"/>
+      <c r="O5" s="235"/>
       <c r="P5" s="61" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/07</v>
       </c>
-      <c r="Q5" s="230"/>
-      <c r="R5" s="223"/>
+      <c r="Q5" s="231"/>
+      <c r="R5" s="224"/>
     </row>
     <row r="6" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -7430,7 +7431,7 @@
       <c r="E64" s="64" t="s">
         <v>190</v>
       </c>
-      <c r="F64" s="64" t="s">
+      <c r="F64" s="239" t="s">
         <v>191</v>
       </c>
       <c r="G64" s="86">
@@ -8313,94 +8314,102 @@
     </row>
     <row r="83" spans="2:18" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="84" spans="2:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E84" s="220" t="str">
+      <c r="E84" s="211" t="str">
         <f>RESUMEN!A14</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="F84" s="213"/>
-      <c r="G84" s="213"/>
-      <c r="H84" s="213"/>
-      <c r="I84" s="213"/>
-      <c r="J84" s="213"/>
-      <c r="K84" s="213"/>
-      <c r="L84" s="213"/>
-      <c r="M84" s="213"/>
-      <c r="N84" s="213"/>
-      <c r="O84" s="213"/>
-      <c r="P84" s="213"/>
+      <c r="F84" s="212"/>
+      <c r="G84" s="212"/>
+      <c r="H84" s="212"/>
+      <c r="I84" s="212"/>
+      <c r="J84" s="212"/>
+      <c r="K84" s="212"/>
+      <c r="L84" s="212"/>
+      <c r="M84" s="212"/>
+      <c r="N84" s="212"/>
+      <c r="O84" s="212"/>
+      <c r="P84" s="212"/>
     </row>
     <row r="85" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E85" s="213"/>
-      <c r="F85" s="213"/>
-      <c r="G85" s="213"/>
-      <c r="H85" s="213"/>
-      <c r="I85" s="213"/>
-      <c r="J85" s="213"/>
-      <c r="K85" s="213"/>
-      <c r="L85" s="213"/>
-      <c r="M85" s="213"/>
-      <c r="N85" s="213"/>
-      <c r="O85" s="213"/>
-      <c r="P85" s="213"/>
+      <c r="E85" s="212"/>
+      <c r="F85" s="212"/>
+      <c r="G85" s="212"/>
+      <c r="H85" s="212"/>
+      <c r="I85" s="212"/>
+      <c r="J85" s="212"/>
+      <c r="K85" s="212"/>
+      <c r="L85" s="212"/>
+      <c r="M85" s="212"/>
+      <c r="N85" s="212"/>
+      <c r="O85" s="212"/>
+      <c r="P85" s="212"/>
     </row>
     <row r="86" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E86" s="213"/>
-      <c r="F86" s="213"/>
-      <c r="G86" s="213"/>
-      <c r="H86" s="213"/>
-      <c r="I86" s="213"/>
-      <c r="J86" s="213"/>
-      <c r="K86" s="213"/>
-      <c r="L86" s="213"/>
-      <c r="M86" s="213"/>
-      <c r="N86" s="213"/>
-      <c r="O86" s="213"/>
-      <c r="P86" s="213"/>
+      <c r="E86" s="212"/>
+      <c r="F86" s="212"/>
+      <c r="G86" s="212"/>
+      <c r="H86" s="212"/>
+      <c r="I86" s="212"/>
+      <c r="J86" s="212"/>
+      <c r="K86" s="212"/>
+      <c r="L86" s="212"/>
+      <c r="M86" s="212"/>
+      <c r="N86" s="212"/>
+      <c r="O86" s="212"/>
+      <c r="P86" s="212"/>
     </row>
     <row r="87" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E87" s="213"/>
-      <c r="F87" s="213"/>
-      <c r="G87" s="213"/>
-      <c r="H87" s="213"/>
-      <c r="I87" s="213"/>
-      <c r="J87" s="213"/>
-      <c r="K87" s="213"/>
-      <c r="L87" s="213"/>
-      <c r="M87" s="213"/>
-      <c r="N87" s="213"/>
-      <c r="O87" s="213"/>
-      <c r="P87" s="213"/>
+      <c r="E87" s="212"/>
+      <c r="F87" s="212"/>
+      <c r="G87" s="212"/>
+      <c r="H87" s="212"/>
+      <c r="I87" s="212"/>
+      <c r="J87" s="212"/>
+      <c r="K87" s="212"/>
+      <c r="L87" s="212"/>
+      <c r="M87" s="212"/>
+      <c r="N87" s="212"/>
+      <c r="O87" s="212"/>
+      <c r="P87" s="212"/>
     </row>
     <row r="88" spans="2:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E88" s="213"/>
-      <c r="F88" s="213"/>
-      <c r="G88" s="213"/>
-      <c r="H88" s="213"/>
-      <c r="I88" s="213"/>
-      <c r="J88" s="213"/>
-      <c r="K88" s="213"/>
-      <c r="L88" s="213"/>
-      <c r="M88" s="213"/>
-      <c r="N88" s="213"/>
-      <c r="O88" s="213"/>
-      <c r="P88" s="213"/>
+      <c r="E88" s="212"/>
+      <c r="F88" s="212"/>
+      <c r="G88" s="212"/>
+      <c r="H88" s="212"/>
+      <c r="I88" s="212"/>
+      <c r="J88" s="212"/>
+      <c r="K88" s="212"/>
+      <c r="L88" s="212"/>
+      <c r="M88" s="212"/>
+      <c r="N88" s="212"/>
+      <c r="O88" s="212"/>
+      <c r="P88" s="212"/>
     </row>
     <row r="89" spans="2:18" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E89" s="213"/>
-      <c r="F89" s="213"/>
-      <c r="G89" s="213"/>
-      <c r="H89" s="213"/>
-      <c r="I89" s="213"/>
-      <c r="J89" s="213"/>
-      <c r="K89" s="213"/>
-      <c r="L89" s="213"/>
-      <c r="M89" s="213"/>
-      <c r="N89" s="213"/>
-      <c r="O89" s="213"/>
-      <c r="P89" s="213"/>
+      <c r="E89" s="212"/>
+      <c r="F89" s="212"/>
+      <c r="G89" s="212"/>
+      <c r="H89" s="212"/>
+      <c r="I89" s="212"/>
+      <c r="J89" s="212"/>
+      <c r="K89" s="212"/>
+      <c r="L89" s="212"/>
+      <c r="M89" s="212"/>
+      <c r="N89" s="212"/>
+      <c r="O89" s="212"/>
+      <c r="P89" s="212"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="G1:P1"/>
+    <mergeCell ref="Q4:Q5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:N5"/>
     <mergeCell ref="E84:P89"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="J4:J5"/>
@@ -8412,14 +8421,6 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F4:F5"/>
     <mergeCell ref="H4:H5"/>
-    <mergeCell ref="R4:R5"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="G1:P1"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:N5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -8433,7 +8434,7 @@
   <sheetData>
     <row r="5" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C5" s="192" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
